--- a/docs/2/GCALIT-Mercury-CY2025.xlsx
+++ b/docs/2/GCALIT-Mercury-CY2025.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00;[Red]-#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -55,12 +56,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -133,7 +136,7 @@
           <t xml:space="preserve">Domestic and international client and affiliate receipts</t>
         </is>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="5">
         <v>13</v>
       </c>
       <c r="D5" s="2">
@@ -151,7 +154,7 @@
           <t xml:space="preserve">YouTube partner payments, an affiliate ACH credit and account-verification micro-deposits</t>
         </is>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="5">
         <v>7</v>
       </c>
       <c r="D6" s="2">
@@ -169,7 +172,7 @@
           <t xml:space="preserve">Cashback credited to the checking account</t>
         </is>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="5">
         <v>2</v>
       </c>
       <c r="D7" s="2">
@@ -182,10 +185,12 @@
           <t xml:space="preserve">TOTAL MONEY IN</t>
         </is>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
+        <f>SUM(C5:C7)</f>
         <v>22</v>
       </c>
       <c r="D8" s="3">
+        <f>SUM(D5:D7)</f>
         <v>36730.05</v>
       </c>
     </row>
@@ -208,7 +213,7 @@
           <t xml:space="preserve">Google Ads invoices, accountancy and platform fees</t>
         </is>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="5">
         <v>9</v>
       </c>
       <c r="D11" s="2">
@@ -226,7 +231,7 @@
           <t xml:space="preserve">Autopay moving cash out of the bank to settle the credit card</t>
         </is>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="5">
         <v>2</v>
       </c>
       <c r="D12" s="2">
@@ -244,98 +249,86 @@
           <t xml:space="preserve">Every dollar that left the bank, card payments included</t>
         </is>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
+        <f>SUM(C11:C12)</f>
         <v>11</v>
       </c>
       <c r="D13" s="3">
+        <f>SUM(D11:D12)</f>
         <v>-15663.38</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    of which expenses</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paid to suppliers, platforms and services</t>
-        </is>
-      </c>
-      <c r="C14" s="2">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2">
-        <v>-15341.23</v>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    of which sent to card</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Moved to the Mercury IO card, then spent from it</t>
-        </is>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>-322.15</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NET CHANGE FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total money in less total money out</t>
+        </is>
+      </c>
+      <c r="C15" s="6">
+        <v>33</v>
+      </c>
+      <c r="D15" s="3">
+        <f>D8+D13</f>
+        <v>21066.67</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">NET CHANGE FOR THE YEAR</t>
+          <t xml:space="preserve">CLOSING BALANCE — 31 December 2025</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total money in less total money out</t>
-        </is>
-      </c>
-      <c r="C17" s="3">
-        <v>33</v>
+          <t xml:space="preserve">Mercury's own ending balance on the statement for 01–31 December 2025</t>
+        </is>
       </c>
       <c r="D17" s="3">
-        <v>21066.67</v>
+        <f>D2+D15</f>
+        <v>32120.51</v>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLOSING BALANCE — 31 December 2025</t>
+          <t xml:space="preserve">PEAK BALANCE — 31 July 2025</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury's own ending balance on the statement for 01–31 December 2025</t>
+          <t xml:space="preserve">Highest balance held at any point in 2025 — the maximum of the Daily sheet</t>
         </is>
       </c>
       <c r="D19" s="3">
-        <v>32120.51</v>
+        <f>MAX(Daily!E2:E366)</f>
+        <v>35157.93</v>
       </c>
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PEAK BALANCE — 31 July 2025</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The highest balance the account held at any point in 2025</t>
-        </is>
-      </c>
-      <c r="D21" s="3">
-        <v>35157.93</v>
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total expense incurred in 2025</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outgoing payments plus what the card itself spent — see the Reconciliation sheet</t>
+        </is>
+      </c>
+      <c r="C21" s="5">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2">
+        <v>-15663.38</v>
       </c>
     </row>
   </sheetData>
@@ -345,9 +338,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="30.00" customWidth="1"/>
+    <col min="1" max="1" width="34.73" customWidth="1"/>
     <col min="2" max="2" width="56.76" customWidth="1"/>
-    <col min="3" max="3" width="21.49" customWidth="1"/>
+    <col min="3" max="3" width="32.84" customWidth="1"/>
     <col min="4" max="4" width="18.92" customWidth="1"/>
   </cols>
   <sheetData>
@@ -390,6 +383,7 @@
         </is>
       </c>
       <c r="D2" s="3">
+        <f>MAX(Daily!E2:E366)</f>
         <v>35157.93</v>
       </c>
     </row>
@@ -402,7 +396,7 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The day the balance first hit that figure</t>
+          <t xml:space="preserve">The day the balance first closed at that figure</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -411,6 +405,7 @@
         </is>
       </c>
       <c r="D4" s="2">
+        <f>D2</f>
         <v>35157.93</v>
       </c>
     </row>
@@ -422,7 +417,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">It stayed at the peak for 4 days, the next movement being the first debit after it</t>
+          <t xml:space="preserve">It stayed there for 4 days; the next movement was the first debit after it</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -431,18 +426,19 @@
         </is>
       </c>
       <c r="D5" s="2">
+        <f>D2</f>
         <v>35157.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caused by</t>
+          <t xml:space="preserve">Tipped to the peak by</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICKSTACK LTD. — Incoming wire (international)</t>
+          <t xml:space="preserve">CLICKSTACK LTD. — Incoming wire (international). The marginal credit that set the exact maximum, not what built it.</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -462,7 +458,7 @@
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The balance the moment before that credit landed</t>
+          <t xml:space="preserve">Where the balance stood the moment before that credit landed</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -471,6 +467,7 @@
         </is>
       </c>
       <c r="D7" s="2">
+        <f>D2-D6</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -482,7 +479,7 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL — Outgoing payment</t>
+          <t xml:space="preserve">Google LLC — Outgoing payment</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -511,6 +508,7 @@
         </is>
       </c>
       <c r="D9" s="2">
+        <f>D2+D8</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -523,7 +521,7 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highest point reached at any moment, in Mercury's own posting order — the same figure, so no intra-day spike sits above the end-of-day peak</t>
+          <t xml:space="preserve">Highest point at any moment, in Mercury's own posting order — the same figure</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -532,6 +530,7 @@
         </is>
       </c>
       <c r="D11" s="2">
+        <f>D2</f>
         <v>35157.93</v>
       </c>
     </row>
@@ -544,15 +543,16 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lowest end-of-day balance in 2025</t>
+          <t xml:space="preserve">Held 6 days — and it is the opening balance: no day closed below where the year began</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 January 2025</t>
+          <t xml:space="preserve">1 January 2025 – 6 January 2025</t>
         </is>
       </c>
       <c r="D13" s="2">
+        <f>MIN(Daily!E2:E366)</f>
         <v>11053.84</v>
       </c>
     </row>
@@ -573,6 +573,7 @@
         </is>
       </c>
       <c r="D14" s="2">
+        <f>AVERAGE(Daily!E2:E366)</f>
         <v>26110.17</v>
       </c>
     </row>
@@ -593,6 +594,7 @@
         </is>
       </c>
       <c r="D15" s="2">
+        <f>Summary!D2</f>
         <v>11053.84</v>
       </c>
     </row>
@@ -613,6 +615,7 @@
         </is>
       </c>
       <c r="D16" s="2">
+        <f>Summary!D17</f>
         <v>32120.51</v>
       </c>
     </row>
@@ -628,6 +631,7 @@
         </is>
       </c>
       <c r="D17" s="2">
+        <f>D2-D16</f>
         <v>3037.42</v>
       </c>
     </row>
@@ -643,6 +647,7 @@
         </is>
       </c>
       <c r="D18" s="2">
+        <f>D2-D15</f>
         <v>24104.09</v>
       </c>
     </row>
@@ -650,243 +655,310 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days spent at or above</t>
+          <t xml:space="preserve">Days closing at or above $35,000</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many of the 365 days closed at or above each level. The figure in the last column is the threshold, not an amount held.</t>
+          <t xml:space="preserve">How many of the 365 days closed at or above that level</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">4 days</t>
         </is>
-      </c>
-      <c r="D20" s="2">
-        <v>35000.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days spent at or above</t>
+          <t xml:space="preserve">Days closing at or above $30,000</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">146 days</t>
         </is>
-      </c>
-      <c r="D21" s="2">
-        <v>30000.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days spent at or above</t>
+          <t xml:space="preserve">Days closing at or above $25,000</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">274 days</t>
         </is>
-      </c>
-      <c r="D22" s="2">
-        <v>25000.0</v>
       </c>
     </row>
     <row r="23"/>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEAK BY MONTH</t>
+          <t xml:space="preserve">WHICH CLOCK THIS IS ON</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highest end-of-day balance inside each month</t>
+          <t xml:space="preserve">Every date here is UTC — the clock all 24 of Mercury's own statements reconcile on</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">  January 2025</t>
+          <t xml:space="preserve">  Margin at the start of the year</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hours between 1 Jan 2025 00:00 UTC and the nearest transaction either side</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 January 2025</t>
-        </is>
-      </c>
-      <c r="D25" s="2">
-        <v>13303.84</v>
+          <t xml:space="preserve">163.57 hours</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">  February 2025</t>
+          <t xml:space="preserve">  Margin at the end of the year</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hours to the nearest transaction either side — wider than any timezone, so the closing balance is the same on every clock</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 February 2025</t>
-        </is>
-      </c>
-      <c r="D26" s="2">
-        <v>13303.84</v>
+          <t xml:space="preserve">12.01 hours</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  March 2025</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26 March 2025</t>
-        </is>
-      </c>
-      <c r="D27" s="2">
-        <v>16985.4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  April 2025</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 April 2025</t>
-        </is>
-      </c>
-      <c r="D28" s="2">
-        <v>28997.24</v>
-      </c>
-    </row>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Margin on the PEAK DATE</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The peak AMOUNT is the same on any clock, the DATE is not — see the Reconciliation sheet</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.03 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  May 2025</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 May 2025</t>
-        </is>
-      </c>
-      <c r="D29" s="2">
-        <v>28996.2</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEAK BY MONTH</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Highest end-of-day balance inside each month</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">  June 2025</t>
+          <t xml:space="preserve">  January 2025</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">27 June 2025</t>
+          <t xml:space="preserve">7 January 2025</t>
         </is>
       </c>
       <c r="D30" s="2">
-        <v>29323.2</v>
+        <f>MAX(Daily!E2:E32)</f>
+        <v>13303.84</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  July 2025</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31 July 2025</t>
-        </is>
-      </c>
-      <c r="D31" s="3">
-        <v>35157.93</v>
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  February 2025</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 February 2025</t>
+        </is>
+      </c>
+      <c r="D31" s="2">
+        <f>MAX(Daily!E33:E60)</f>
+        <v>13303.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">  August 2025</t>
+          <t xml:space="preserve">  March 2025</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 August 2025</t>
+          <t xml:space="preserve">26 March 2025</t>
         </is>
       </c>
       <c r="D32" s="2">
-        <v>35157.93</v>
+        <f>MAX(Daily!E61:E91)</f>
+        <v>16985.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">  September 2025</t>
+          <t xml:space="preserve">  April 2025</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 September 2025</t>
+          <t xml:space="preserve">7 April 2025</t>
         </is>
       </c>
       <c r="D33" s="2">
-        <v>34248.63</v>
+        <f>MAX(Daily!E92:E121)</f>
+        <v>28997.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">  October 2025</t>
+          <t xml:space="preserve">  May 2025</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 October 2025</t>
+          <t xml:space="preserve">1 May 2025</t>
         </is>
       </c>
       <c r="D34" s="2">
-        <v>34248.63</v>
+        <f>MAX(Daily!E122:E152)</f>
+        <v>28996.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">  June 2025</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27 June 2025</t>
+        </is>
+      </c>
+      <c r="D35" s="2">
+        <f>MAX(Daily!E153:E182)</f>
+        <v>29323.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  July 2025</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31 July 2025</t>
+        </is>
+      </c>
+      <c r="D36" s="3">
+        <f>MAX(Daily!E183:E213)</f>
+        <v>35157.93</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  August 2025</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 August 2025</t>
+        </is>
+      </c>
+      <c r="D37" s="3">
+        <f>MAX(Daily!E214:E244)</f>
+        <v>35157.93</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  September 2025</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 September 2025</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
+        <f>MAX(Daily!E245:E274)</f>
+        <v>34248.63</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  October 2025</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 October 2025</t>
+        </is>
+      </c>
+      <c r="D39" s="2">
+        <f>MAX(Daily!E275:E305)</f>
+        <v>34248.63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">  November 2025</t>
         </is>
       </c>
-      <c r="C35" s="0" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">21 November 2025</t>
         </is>
       </c>
-      <c r="D35" s="2">
+      <c r="D40" s="2">
+        <f>MAX(Daily!E306:E335)</f>
         <v>30713.57</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="0" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">  December 2025</t>
         </is>
       </c>
-      <c r="C36" s="0" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">31 December 2025</t>
         </is>
       </c>
-      <c r="D36" s="2">
+      <c r="D41" s="2">
+        <f>MAX(Daily!E336:E366)</f>
         <v>32120.51</v>
       </c>
     </row>
@@ -948,10 +1020,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="5">
         <v>0</v>
       </c>
       <c r="E2" s="2">
+        <f>Summary!D2+D2</f>
         <v>11053.84</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
@@ -971,11 +1044,17 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="5">
         <v>0</v>
       </c>
       <c r="E3" s="2">
+        <f>E2+D3</f>
         <v>11053.84</v>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low held</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -989,11 +1068,17 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="5">
         <v>0</v>
       </c>
       <c r="E4" s="2">
+        <f>E3+D4</f>
         <v>11053.84</v>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low held</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1007,11 +1092,17 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="E5" s="2">
+        <f>E4+D5</f>
         <v>11053.84</v>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low held</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1025,11 +1116,17 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="5">
         <v>0</v>
       </c>
       <c r="E6" s="2">
+        <f>E5+D6</f>
         <v>11053.84</v>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low held</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1043,11 +1140,17 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="5">
         <v>0</v>
       </c>
       <c r="E7" s="2">
+        <f>E6+D7</f>
         <v>11053.84</v>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low held</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1061,13 +1164,14 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="5">
         <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>2250.0</v>
       </c>
       <c r="E8" s="2">
+        <f>E7+D8</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1082,10 +1186,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="5">
         <v>0</v>
       </c>
       <c r="E9" s="2">
+        <f>E8+D9</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1100,10 +1205,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="5">
         <v>0</v>
       </c>
       <c r="E10" s="2">
+        <f>E9+D10</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1118,10 +1224,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="E11" s="2">
+        <f>E10+D11</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1136,10 +1243,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="5">
         <v>0</v>
       </c>
       <c r="E12" s="2">
+        <f>E11+D12</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1154,10 +1262,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="5">
         <v>0</v>
       </c>
       <c r="E13" s="2">
+        <f>E12+D13</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1172,10 +1281,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="5">
         <v>0</v>
       </c>
       <c r="E14" s="2">
+        <f>E13+D14</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1190,10 +1300,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="5">
         <v>0</v>
       </c>
       <c r="E15" s="2">
+        <f>E14+D15</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1208,10 +1319,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="5">
         <v>0</v>
       </c>
       <c r="E16" s="2">
+        <f>E15+D16</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1226,10 +1338,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="5">
         <v>0</v>
       </c>
       <c r="E17" s="2">
+        <f>E16+D17</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1244,10 +1357,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="5">
         <v>0</v>
       </c>
       <c r="E18" s="2">
+        <f>E17+D18</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1262,10 +1376,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="5">
         <v>0</v>
       </c>
       <c r="E19" s="2">
+        <f>E18+D19</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1280,10 +1395,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="5">
         <v>0</v>
       </c>
       <c r="E20" s="2">
+        <f>E19+D20</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1298,10 +1414,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="5">
         <v>0</v>
       </c>
       <c r="E21" s="2">
+        <f>E20+D21</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1316,10 +1433,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="5">
         <v>0</v>
       </c>
       <c r="E22" s="2">
+        <f>E21+D22</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1334,10 +1452,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="5">
         <v>0</v>
       </c>
       <c r="E23" s="2">
+        <f>E22+D23</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1352,10 +1471,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="5">
         <v>0</v>
       </c>
       <c r="E24" s="2">
+        <f>E23+D24</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1370,10 +1490,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="5">
         <v>0</v>
       </c>
       <c r="E25" s="2">
+        <f>E24+D25</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1388,10 +1509,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="5">
         <v>0</v>
       </c>
       <c r="E26" s="2">
+        <f>E25+D26</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1406,10 +1528,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="5">
         <v>0</v>
       </c>
       <c r="E27" s="2">
+        <f>E26+D27</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1424,10 +1547,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="5">
         <v>0</v>
       </c>
       <c r="E28" s="2">
+        <f>E27+D28</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1442,10 +1566,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="5">
         <v>0</v>
       </c>
       <c r="E29" s="2">
+        <f>E28+D29</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1460,10 +1585,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="5">
         <v>0</v>
       </c>
       <c r="E30" s="2">
+        <f>E29+D30</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1478,10 +1604,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="5">
         <v>0</v>
       </c>
       <c r="E31" s="2">
+        <f>E30+D31</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1496,10 +1623,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="5">
         <v>0</v>
       </c>
       <c r="E32" s="2">
+        <f>E31+D32</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1514,10 +1642,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="5">
         <v>0</v>
       </c>
       <c r="E33" s="2">
+        <f>E32+D33</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1532,10 +1661,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="5">
         <v>0</v>
       </c>
       <c r="E34" s="2">
+        <f>E33+D34</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1550,10 +1680,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="5">
         <v>0</v>
       </c>
       <c r="E35" s="2">
+        <f>E34+D35</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1568,10 +1699,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="5">
         <v>0</v>
       </c>
       <c r="E36" s="2">
+        <f>E35+D36</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1586,10 +1718,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="5">
         <v>0</v>
       </c>
       <c r="E37" s="2">
+        <f>E36+D37</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1604,10 +1737,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="5">
         <v>0</v>
       </c>
       <c r="E38" s="2">
+        <f>E37+D38</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1622,10 +1756,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="5">
         <v>0</v>
       </c>
       <c r="E39" s="2">
+        <f>E38+D39</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1640,10 +1775,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="5">
         <v>0</v>
       </c>
       <c r="E40" s="2">
+        <f>E39+D40</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1658,10 +1794,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="5">
         <v>0</v>
       </c>
       <c r="E41" s="2">
+        <f>E40+D41</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1676,10 +1813,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="5">
         <v>0</v>
       </c>
       <c r="E42" s="2">
+        <f>E41+D42</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1694,10 +1832,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="5">
         <v>0</v>
       </c>
       <c r="E43" s="2">
+        <f>E42+D43</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1712,10 +1851,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="5">
         <v>0</v>
       </c>
       <c r="E44" s="2">
+        <f>E43+D44</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1730,10 +1870,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="5">
         <v>0</v>
       </c>
       <c r="E45" s="2">
+        <f>E44+D45</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1748,10 +1889,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="5">
         <v>0</v>
       </c>
       <c r="E46" s="2">
+        <f>E45+D46</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1766,10 +1908,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="5">
         <v>0</v>
       </c>
       <c r="E47" s="2">
+        <f>E46+D47</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1784,10 +1927,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="5">
         <v>0</v>
       </c>
       <c r="E48" s="2">
+        <f>E47+D48</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1802,10 +1946,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="5">
         <v>0</v>
       </c>
       <c r="E49" s="2">
+        <f>E48+D49</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1820,10 +1965,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="5">
         <v>0</v>
       </c>
       <c r="E50" s="2">
+        <f>E49+D50</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1838,10 +1984,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="5">
         <v>0</v>
       </c>
       <c r="E51" s="2">
+        <f>E50+D51</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1856,10 +2003,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="5">
         <v>0</v>
       </c>
       <c r="E52" s="2">
+        <f>E51+D52</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1874,10 +2022,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="5">
         <v>0</v>
       </c>
       <c r="E53" s="2">
+        <f>E52+D53</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1892,10 +2041,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="5">
         <v>0</v>
       </c>
       <c r="E54" s="2">
+        <f>E53+D54</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1910,10 +2060,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="5">
         <v>0</v>
       </c>
       <c r="E55" s="2">
+        <f>E54+D55</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1928,10 +2079,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="5">
         <v>0</v>
       </c>
       <c r="E56" s="2">
+        <f>E55+D56</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1946,10 +2098,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="5">
         <v>0</v>
       </c>
       <c r="E57" s="2">
+        <f>E56+D57</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1964,10 +2117,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="5">
         <v>0</v>
       </c>
       <c r="E58" s="2">
+        <f>E57+D58</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -1982,10 +2136,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="5">
         <v>0</v>
       </c>
       <c r="E59" s="2">
+        <f>E58+D59</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2000,10 +2155,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="5">
         <v>0</v>
       </c>
       <c r="E60" s="2">
+        <f>E59+D60</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2018,10 +2174,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="5">
         <v>0</v>
       </c>
       <c r="E61" s="2">
+        <f>E60+D61</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2036,10 +2193,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="5">
         <v>0</v>
       </c>
       <c r="E62" s="2">
+        <f>E61+D62</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2054,10 +2212,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="5">
         <v>0</v>
       </c>
       <c r="E63" s="2">
+        <f>E62+D63</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2072,10 +2231,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="5">
         <v>0</v>
       </c>
       <c r="E64" s="2">
+        <f>E63+D64</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2090,10 +2250,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="5">
         <v>0</v>
       </c>
       <c r="E65" s="2">
+        <f>E64+D65</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2108,10 +2269,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="5">
         <v>0</v>
       </c>
       <c r="E66" s="2">
+        <f>E65+D66</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2126,10 +2288,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="5">
         <v>0</v>
       </c>
       <c r="E67" s="2">
+        <f>E66+D67</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2144,10 +2307,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="5">
         <v>0</v>
       </c>
       <c r="E68" s="2">
+        <f>E67+D68</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2162,10 +2326,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="5">
         <v>0</v>
       </c>
       <c r="E69" s="2">
+        <f>E68+D69</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2180,10 +2345,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="5">
         <v>0</v>
       </c>
       <c r="E70" s="2">
+        <f>E69+D70</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2198,10 +2364,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="5">
         <v>0</v>
       </c>
       <c r="E71" s="2">
+        <f>E70+D71</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2216,10 +2383,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="5">
         <v>0</v>
       </c>
       <c r="E72" s="2">
+        <f>E71+D72</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -2234,13 +2402,14 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="5">
         <v>1</v>
       </c>
       <c r="D73" s="2">
         <v>-16.58</v>
       </c>
       <c r="E73" s="2">
+        <f>E72+D73</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2255,10 +2424,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="5">
         <v>0</v>
       </c>
       <c r="E74" s="2">
+        <f>E73+D74</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2273,10 +2443,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="5">
         <v>0</v>
       </c>
       <c r="E75" s="2">
+        <f>E74+D75</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2291,10 +2462,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="5">
         <v>0</v>
       </c>
       <c r="E76" s="2">
+        <f>E75+D76</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2309,10 +2481,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="5">
         <v>0</v>
       </c>
       <c r="E77" s="2">
+        <f>E76+D77</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2327,10 +2500,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="5">
         <v>0</v>
       </c>
       <c r="E78" s="2">
+        <f>E77+D78</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2345,10 +2519,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="5">
         <v>0</v>
       </c>
       <c r="E79" s="2">
+        <f>E78+D79</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2363,10 +2538,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="5">
         <v>0</v>
       </c>
       <c r="E80" s="2">
+        <f>E79+D80</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2381,10 +2557,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="5">
         <v>0</v>
       </c>
       <c r="E81" s="2">
+        <f>E80+D81</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2399,10 +2576,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="5">
         <v>0</v>
       </c>
       <c r="E82" s="2">
+        <f>E81+D82</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2417,10 +2595,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="5">
         <v>0</v>
       </c>
       <c r="E83" s="2">
+        <f>E82+D83</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -2435,13 +2614,14 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="5">
         <v>1</v>
       </c>
       <c r="D84" s="2">
         <v>-90.0</v>
       </c>
       <c r="E84" s="2">
+        <f>E83+D84</f>
         <v>13197.26</v>
       </c>
     </row>
@@ -2456,10 +2636,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="5">
         <v>0</v>
       </c>
       <c r="E85" s="2">
+        <f>E84+D85</f>
         <v>13197.26</v>
       </c>
     </row>
@@ -2474,13 +2655,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="5">
         <v>1</v>
       </c>
       <c r="D86" s="2">
         <v>3788.14</v>
       </c>
       <c r="E86" s="2">
+        <f>E85+D86</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -2495,10 +2677,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="5">
         <v>0</v>
       </c>
       <c r="E87" s="2">
+        <f>E86+D87</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -2513,10 +2696,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C88" s="2">
+      <c r="C88" s="5">
         <v>0</v>
       </c>
       <c r="E88" s="2">
+        <f>E87+D88</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -2531,10 +2715,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="5">
         <v>0</v>
       </c>
       <c r="E89" s="2">
+        <f>E88+D89</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -2549,10 +2734,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="5">
         <v>0</v>
       </c>
       <c r="E90" s="2">
+        <f>E89+D90</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -2567,10 +2753,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="5">
         <v>0</v>
       </c>
       <c r="E91" s="2">
+        <f>E90+D91</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -2585,10 +2772,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="5">
         <v>0</v>
       </c>
       <c r="E92" s="2">
+        <f>E91+D92</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -2603,13 +2791,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="5">
         <v>1</v>
       </c>
       <c r="D93" s="2">
         <v>8548.04</v>
       </c>
       <c r="E93" s="2">
+        <f>E92+D93</f>
         <v>25533.44</v>
       </c>
     </row>
@@ -2624,10 +2813,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C94" s="2">
+      <c r="C94" s="5">
         <v>0</v>
       </c>
       <c r="E94" s="2">
+        <f>E93+D94</f>
         <v>25533.44</v>
       </c>
     </row>
@@ -2642,13 +2832,14 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="5">
         <v>1</v>
       </c>
       <c r="D95" s="2">
         <v>1340.0</v>
       </c>
       <c r="E95" s="2">
+        <f>E94+D95</f>
         <v>26873.44</v>
       </c>
     </row>
@@ -2663,10 +2854,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="5">
         <v>0</v>
       </c>
       <c r="E96" s="2">
+        <f>E95+D96</f>
         <v>26873.44</v>
       </c>
     </row>
@@ -2681,10 +2873,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="5">
         <v>0</v>
       </c>
       <c r="E97" s="2">
+        <f>E96+D97</f>
         <v>26873.44</v>
       </c>
     </row>
@@ -2699,13 +2892,14 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="5">
         <v>1</v>
       </c>
       <c r="D98" s="2">
         <v>2123.8</v>
       </c>
       <c r="E98" s="2">
+        <f>E97+D98</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2720,10 +2914,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C99" s="2">
+      <c r="C99" s="5">
         <v>0</v>
       </c>
       <c r="E99" s="2">
+        <f>E98+D99</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2738,10 +2933,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C100" s="2">
+      <c r="C100" s="5">
         <v>0</v>
       </c>
       <c r="E100" s="2">
+        <f>E99+D100</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2756,10 +2952,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="5">
         <v>0</v>
       </c>
       <c r="E101" s="2">
+        <f>E100+D101</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2774,10 +2971,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C102" s="2">
+      <c r="C102" s="5">
         <v>0</v>
       </c>
       <c r="E102" s="2">
+        <f>E101+D102</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2792,10 +2990,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="5">
         <v>0</v>
       </c>
       <c r="E103" s="2">
+        <f>E102+D103</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2810,10 +3009,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="5">
         <v>0</v>
       </c>
       <c r="E104" s="2">
+        <f>E103+D104</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2828,10 +3028,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="5">
         <v>0</v>
       </c>
       <c r="E105" s="2">
+        <f>E104+D105</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2846,10 +3047,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C106" s="2">
+      <c r="C106" s="5">
         <v>0</v>
       </c>
       <c r="E106" s="2">
+        <f>E105+D106</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2864,10 +3066,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="5">
         <v>0</v>
       </c>
       <c r="E107" s="2">
+        <f>E106+D107</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2882,10 +3085,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="5">
         <v>0</v>
       </c>
       <c r="E108" s="2">
+        <f>E107+D108</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2900,10 +3104,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="5">
         <v>0</v>
       </c>
       <c r="E109" s="2">
+        <f>E108+D109</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2918,10 +3123,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C110" s="2">
+      <c r="C110" s="5">
         <v>0</v>
       </c>
       <c r="E110" s="2">
+        <f>E109+D110</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2936,10 +3142,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="5">
         <v>0</v>
       </c>
       <c r="E111" s="2">
+        <f>E110+D111</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -2954,13 +3161,14 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C112" s="2">
+      <c r="C112" s="5">
         <v>2</v>
       </c>
       <c r="D112" s="2">
         <v>-1.04</v>
       </c>
       <c r="E112" s="2">
+        <f>E111+D112</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -2975,10 +3183,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="5">
         <v>0</v>
       </c>
       <c r="E113" s="2">
+        <f>E112+D113</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -2993,10 +3202,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C114" s="2">
+      <c r="C114" s="5">
         <v>0</v>
       </c>
       <c r="E114" s="2">
+        <f>E113+D114</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3011,10 +3221,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C115" s="2">
+      <c r="C115" s="5">
         <v>0</v>
       </c>
       <c r="E115" s="2">
+        <f>E114+D115</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3029,10 +3240,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="5">
         <v>0</v>
       </c>
       <c r="E116" s="2">
+        <f>E115+D116</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3047,10 +3259,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="5">
         <v>0</v>
       </c>
       <c r="E117" s="2">
+        <f>E116+D117</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3065,10 +3278,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C118" s="2">
+      <c r="C118" s="5">
         <v>0</v>
       </c>
       <c r="E118" s="2">
+        <f>E117+D118</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3083,10 +3297,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="5">
         <v>0</v>
       </c>
       <c r="E119" s="2">
+        <f>E118+D119</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3101,10 +3316,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="5">
         <v>0</v>
       </c>
       <c r="E120" s="2">
+        <f>E119+D120</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3119,10 +3335,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="5">
         <v>0</v>
       </c>
       <c r="E121" s="2">
+        <f>E120+D121</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3137,10 +3354,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C122" s="2">
+      <c r="C122" s="5">
         <v>0</v>
       </c>
       <c r="E122" s="2">
+        <f>E121+D122</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3155,10 +3373,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="5">
         <v>0</v>
       </c>
       <c r="E123" s="2">
+        <f>E122+D123</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3173,10 +3392,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C124" s="2">
+      <c r="C124" s="5">
         <v>0</v>
       </c>
       <c r="E124" s="2">
+        <f>E123+D124</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3191,10 +3411,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="5">
         <v>0</v>
       </c>
       <c r="E125" s="2">
+        <f>E124+D125</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3209,10 +3430,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C126" s="2">
+      <c r="C126" s="5">
         <v>0</v>
       </c>
       <c r="E126" s="2">
+        <f>E125+D126</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3227,10 +3449,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="5">
         <v>0</v>
       </c>
       <c r="E127" s="2">
+        <f>E126+D127</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3245,10 +3468,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="5">
         <v>0</v>
       </c>
       <c r="E128" s="2">
+        <f>E127+D128</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3263,10 +3487,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="5">
         <v>0</v>
       </c>
       <c r="E129" s="2">
+        <f>E128+D129</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3281,10 +3506,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C130" s="2">
+      <c r="C130" s="5">
         <v>0</v>
       </c>
       <c r="E130" s="2">
+        <f>E129+D130</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3299,10 +3525,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="5">
         <v>0</v>
       </c>
       <c r="E131" s="2">
+        <f>E130+D131</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3317,10 +3544,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C132" s="2">
+      <c r="C132" s="5">
         <v>0</v>
       </c>
       <c r="E132" s="2">
+        <f>E131+D132</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3335,10 +3563,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="5">
         <v>0</v>
       </c>
       <c r="E133" s="2">
+        <f>E132+D133</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3353,10 +3582,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="5">
         <v>0</v>
       </c>
       <c r="E134" s="2">
+        <f>E133+D134</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3371,10 +3601,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C135" s="2">
+      <c r="C135" s="5">
         <v>0</v>
       </c>
       <c r="E135" s="2">
+        <f>E134+D135</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3389,10 +3620,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="5">
         <v>0</v>
       </c>
       <c r="E136" s="2">
+        <f>E135+D136</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3407,10 +3639,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="5">
         <v>0</v>
       </c>
       <c r="E137" s="2">
+        <f>E136+D137</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3425,10 +3658,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C138" s="2">
+      <c r="C138" s="5">
         <v>0</v>
       </c>
       <c r="E138" s="2">
+        <f>E137+D138</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3443,10 +3677,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C139" s="2">
+      <c r="C139" s="5">
         <v>0</v>
       </c>
       <c r="E139" s="2">
+        <f>E138+D139</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3461,10 +3696,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C140" s="2">
+      <c r="C140" s="5">
         <v>0</v>
       </c>
       <c r="E140" s="2">
+        <f>E139+D140</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3479,10 +3715,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C141" s="2">
+      <c r="C141" s="5">
         <v>0</v>
       </c>
       <c r="E141" s="2">
+        <f>E140+D141</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3497,10 +3734,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C142" s="2">
+      <c r="C142" s="5">
         <v>0</v>
       </c>
       <c r="E142" s="2">
+        <f>E141+D142</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3515,10 +3753,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="5">
         <v>0</v>
       </c>
       <c r="E143" s="2">
+        <f>E142+D143</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3533,10 +3772,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C144" s="2">
+      <c r="C144" s="5">
         <v>0</v>
       </c>
       <c r="E144" s="2">
+        <f>E143+D144</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3551,10 +3791,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C145" s="2">
+      <c r="C145" s="5">
         <v>0</v>
       </c>
       <c r="E145" s="2">
+        <f>E144+D145</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3569,10 +3810,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C146" s="2">
+      <c r="C146" s="5">
         <v>0</v>
       </c>
       <c r="E146" s="2">
+        <f>E145+D146</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3587,10 +3829,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C147" s="2">
+      <c r="C147" s="5">
         <v>0</v>
       </c>
       <c r="E147" s="2">
+        <f>E146+D147</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3605,10 +3848,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C148" s="2">
+      <c r="C148" s="5">
         <v>0</v>
       </c>
       <c r="E148" s="2">
+        <f>E147+D148</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3623,10 +3867,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C149" s="2">
+      <c r="C149" s="5">
         <v>0</v>
       </c>
       <c r="E149" s="2">
+        <f>E148+D149</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3641,10 +3886,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C150" s="2">
+      <c r="C150" s="5">
         <v>0</v>
       </c>
       <c r="E150" s="2">
+        <f>E149+D150</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3659,10 +3905,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C151" s="2">
+      <c r="C151" s="5">
         <v>0</v>
       </c>
       <c r="E151" s="2">
+        <f>E150+D151</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3677,10 +3924,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C152" s="2">
+      <c r="C152" s="5">
         <v>0</v>
       </c>
       <c r="E152" s="2">
+        <f>E151+D152</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3695,10 +3943,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C153" s="2">
+      <c r="C153" s="5">
         <v>0</v>
       </c>
       <c r="E153" s="2">
+        <f>E152+D153</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3713,10 +3962,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C154" s="2">
+      <c r="C154" s="5">
         <v>0</v>
       </c>
       <c r="E154" s="2">
+        <f>E153+D154</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3731,10 +3981,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C155" s="2">
+      <c r="C155" s="5">
         <v>0</v>
       </c>
       <c r="E155" s="2">
+        <f>E154+D155</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3749,10 +4000,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C156" s="2">
+      <c r="C156" s="5">
         <v>0</v>
       </c>
       <c r="E156" s="2">
+        <f>E155+D156</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3767,10 +4019,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C157" s="2">
+      <c r="C157" s="5">
         <v>0</v>
       </c>
       <c r="E157" s="2">
+        <f>E156+D157</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3785,10 +4038,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C158" s="2">
+      <c r="C158" s="5">
         <v>0</v>
       </c>
       <c r="E158" s="2">
+        <f>E157+D158</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3803,10 +4057,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C159" s="2">
+      <c r="C159" s="5">
         <v>0</v>
       </c>
       <c r="E159" s="2">
+        <f>E158+D159</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3821,10 +4076,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C160" s="2">
+      <c r="C160" s="5">
         <v>0</v>
       </c>
       <c r="E160" s="2">
+        <f>E159+D160</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3839,10 +4095,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C161" s="2">
+      <c r="C161" s="5">
         <v>0</v>
       </c>
       <c r="E161" s="2">
+        <f>E160+D161</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3857,10 +4114,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C162" s="2">
+      <c r="C162" s="5">
         <v>0</v>
       </c>
       <c r="E162" s="2">
+        <f>E161+D162</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3875,10 +4133,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C163" s="2">
+      <c r="C163" s="5">
         <v>0</v>
       </c>
       <c r="E163" s="2">
+        <f>E162+D163</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3893,10 +4152,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C164" s="2">
+      <c r="C164" s="5">
         <v>0</v>
       </c>
       <c r="E164" s="2">
+        <f>E163+D164</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3911,10 +4171,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C165" s="2">
+      <c r="C165" s="5">
         <v>0</v>
       </c>
       <c r="E165" s="2">
+        <f>E164+D165</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3929,10 +4190,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C166" s="2">
+      <c r="C166" s="5">
         <v>0</v>
       </c>
       <c r="E166" s="2">
+        <f>E165+D166</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3947,10 +4209,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C167" s="2">
+      <c r="C167" s="5">
         <v>0</v>
       </c>
       <c r="E167" s="2">
+        <f>E166+D167</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3965,10 +4228,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C168" s="2">
+      <c r="C168" s="5">
         <v>0</v>
       </c>
       <c r="E168" s="2">
+        <f>E167+D168</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -3983,10 +4247,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C169" s="2">
+      <c r="C169" s="5">
         <v>0</v>
       </c>
       <c r="E169" s="2">
+        <f>E168+D169</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4001,10 +4266,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C170" s="2">
+      <c r="C170" s="5">
         <v>0</v>
       </c>
       <c r="E170" s="2">
+        <f>E169+D170</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4019,10 +4285,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C171" s="2">
+      <c r="C171" s="5">
         <v>0</v>
       </c>
       <c r="E171" s="2">
+        <f>E170+D171</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4037,10 +4304,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C172" s="2">
+      <c r="C172" s="5">
         <v>0</v>
       </c>
       <c r="E172" s="2">
+        <f>E171+D172</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4055,10 +4323,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C173" s="2">
+      <c r="C173" s="5">
         <v>0</v>
       </c>
       <c r="E173" s="2">
+        <f>E172+D173</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4073,10 +4342,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C174" s="2">
+      <c r="C174" s="5">
         <v>0</v>
       </c>
       <c r="E174" s="2">
+        <f>E173+D174</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4091,10 +4361,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C175" s="2">
+      <c r="C175" s="5">
         <v>0</v>
       </c>
       <c r="E175" s="2">
+        <f>E174+D175</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4109,10 +4380,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C176" s="2">
+      <c r="C176" s="5">
         <v>0</v>
       </c>
       <c r="E176" s="2">
+        <f>E175+D176</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4127,10 +4399,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C177" s="2">
+      <c r="C177" s="5">
         <v>0</v>
       </c>
       <c r="E177" s="2">
+        <f>E176+D177</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4145,10 +4418,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C178" s="2">
+      <c r="C178" s="5">
         <v>0</v>
       </c>
       <c r="E178" s="2">
+        <f>E177+D178</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -4163,13 +4437,14 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C179" s="2">
+      <c r="C179" s="5">
         <v>1</v>
       </c>
       <c r="D179" s="2">
         <v>327.0</v>
       </c>
       <c r="E179" s="2">
+        <f>E178+D179</f>
         <v>29323.2</v>
       </c>
     </row>
@@ -4184,10 +4459,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C180" s="2">
+      <c r="C180" s="5">
         <v>0</v>
       </c>
       <c r="E180" s="2">
+        <f>E179+D180</f>
         <v>29323.2</v>
       </c>
     </row>
@@ -4202,10 +4478,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C181" s="2">
+      <c r="C181" s="5">
         <v>0</v>
       </c>
       <c r="E181" s="2">
+        <f>E180+D181</f>
         <v>29323.2</v>
       </c>
     </row>
@@ -4220,13 +4497,14 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C182" s="2">
+      <c r="C182" s="5">
         <v>1</v>
       </c>
       <c r="D182" s="2">
         <v>-6.44</v>
       </c>
       <c r="E182" s="2">
+        <f>E181+D182</f>
         <v>29316.76</v>
       </c>
     </row>
@@ -4241,10 +4519,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C183" s="2">
+      <c r="C183" s="5">
         <v>0</v>
       </c>
       <c r="E183" s="2">
+        <f>E182+D183</f>
         <v>29316.76</v>
       </c>
     </row>
@@ -4259,13 +4538,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C184" s="2">
+      <c r="C184" s="5">
         <v>1</v>
       </c>
       <c r="D184" s="2">
         <v>-2398.97</v>
       </c>
       <c r="E184" s="2">
+        <f>E183+D184</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -4280,10 +4560,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C185" s="2">
+      <c r="C185" s="5">
         <v>0</v>
       </c>
       <c r="E185" s="2">
+        <f>E184+D185</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -4298,10 +4579,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C186" s="2">
+      <c r="C186" s="5">
         <v>0</v>
       </c>
       <c r="E186" s="2">
+        <f>E185+D186</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -4316,10 +4598,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C187" s="2">
+      <c r="C187" s="5">
         <v>0</v>
       </c>
       <c r="E187" s="2">
+        <f>E186+D187</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -4334,10 +4617,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C188" s="2">
+      <c r="C188" s="5">
         <v>0</v>
       </c>
       <c r="E188" s="2">
+        <f>E187+D188</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -4352,10 +4636,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C189" s="2">
+      <c r="C189" s="5">
         <v>0</v>
       </c>
       <c r="E189" s="2">
+        <f>E188+D189</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -4370,10 +4655,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C190" s="2">
+      <c r="C190" s="5">
         <v>0</v>
       </c>
       <c r="E190" s="2">
+        <f>E189+D190</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -4388,13 +4674,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C191" s="2">
+      <c r="C191" s="5">
         <v>1</v>
       </c>
       <c r="D191" s="2">
         <v>6347.78</v>
       </c>
       <c r="E191" s="2">
+        <f>E190+D191</f>
         <v>33265.57</v>
       </c>
     </row>
@@ -4409,10 +4696,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C192" s="2">
+      <c r="C192" s="5">
         <v>0</v>
       </c>
       <c r="E192" s="2">
+        <f>E191+D192</f>
         <v>33265.57</v>
       </c>
     </row>
@@ -4427,10 +4715,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C193" s="2">
+      <c r="C193" s="5">
         <v>0</v>
       </c>
       <c r="E193" s="2">
+        <f>E192+D193</f>
         <v>33265.57</v>
       </c>
     </row>
@@ -4445,13 +4734,14 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C194" s="2">
+      <c r="C194" s="5">
         <v>2</v>
       </c>
       <c r="D194" s="2">
         <v>-237.64</v>
       </c>
       <c r="E194" s="2">
+        <f>E193+D194</f>
         <v>33027.93</v>
       </c>
     </row>
@@ -4466,10 +4756,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C195" s="2">
+      <c r="C195" s="5">
         <v>0</v>
       </c>
       <c r="E195" s="2">
+        <f>E194+D195</f>
         <v>33027.93</v>
       </c>
     </row>
@@ -4484,10 +4775,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C196" s="2">
+      <c r="C196" s="5">
         <v>0</v>
       </c>
       <c r="E196" s="2">
+        <f>E195+D196</f>
         <v>33027.93</v>
       </c>
     </row>
@@ -4502,10 +4794,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C197" s="2">
+      <c r="C197" s="5">
         <v>0</v>
       </c>
       <c r="E197" s="2">
+        <f>E196+D197</f>
         <v>33027.93</v>
       </c>
     </row>
@@ -4520,10 +4813,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C198" s="2">
+      <c r="C198" s="5">
         <v>0</v>
       </c>
       <c r="E198" s="2">
+        <f>E197+D198</f>
         <v>33027.93</v>
       </c>
     </row>
@@ -4538,13 +4832,14 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C199" s="2">
+      <c r="C199" s="5">
         <v>1</v>
       </c>
       <c r="D199" s="2">
         <v>1380.0</v>
       </c>
       <c r="E199" s="2">
+        <f>E198+D199</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4559,10 +4854,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C200" s="2">
+      <c r="C200" s="5">
         <v>0</v>
       </c>
       <c r="E200" s="2">
+        <f>E199+D200</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4577,10 +4873,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C201" s="2">
+      <c r="C201" s="5">
         <v>0</v>
       </c>
       <c r="E201" s="2">
+        <f>E200+D201</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4595,10 +4892,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C202" s="2">
+      <c r="C202" s="5">
         <v>0</v>
       </c>
       <c r="E202" s="2">
+        <f>E201+D202</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4613,10 +4911,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C203" s="2">
+      <c r="C203" s="5">
         <v>0</v>
       </c>
       <c r="E203" s="2">
+        <f>E202+D203</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4631,10 +4930,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C204" s="2">
+      <c r="C204" s="5">
         <v>0</v>
       </c>
       <c r="E204" s="2">
+        <f>E203+D204</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4649,10 +4949,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C205" s="2">
+      <c r="C205" s="5">
         <v>0</v>
       </c>
       <c r="E205" s="2">
+        <f>E204+D205</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4667,10 +4968,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C206" s="2">
+      <c r="C206" s="5">
         <v>0</v>
       </c>
       <c r="E206" s="2">
+        <f>E205+D206</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4685,10 +4987,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C207" s="2">
+      <c r="C207" s="5">
         <v>0</v>
       </c>
       <c r="E207" s="2">
+        <f>E206+D207</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4703,10 +5006,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C208" s="2">
+      <c r="C208" s="5">
         <v>0</v>
       </c>
       <c r="E208" s="2">
+        <f>E207+D208</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4721,10 +5025,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C209" s="2">
+      <c r="C209" s="5">
         <v>0</v>
       </c>
       <c r="E209" s="2">
+        <f>E208+D209</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4739,10 +5044,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C210" s="2">
+      <c r="C210" s="5">
         <v>0</v>
       </c>
       <c r="E210" s="2">
+        <f>E209+D210</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4757,10 +5063,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C211" s="2">
+      <c r="C211" s="5">
         <v>0</v>
       </c>
       <c r="E211" s="2">
+        <f>E210+D211</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4775,10 +5082,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C212" s="2">
+      <c r="C212" s="5">
         <v>0</v>
       </c>
       <c r="E212" s="2">
+        <f>E211+D212</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -4793,13 +5101,14 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C213" s="3">
+      <c r="C213" s="6">
         <v>1</v>
       </c>
       <c r="D213" s="3">
         <v>750.0</v>
       </c>
       <c r="E213" s="3">
+        <f>E212+D213</f>
         <v>35157.93</v>
       </c>
       <c r="F213" s="1" t="inlineStr">
@@ -4819,10 +5128,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C214" s="2">
+      <c r="C214" s="5">
         <v>0</v>
       </c>
       <c r="E214" s="2">
+        <f>E213+D214</f>
         <v>35157.93</v>
       </c>
       <c r="F214" s="0" t="inlineStr">
@@ -4842,10 +5152,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C215" s="2">
+      <c r="C215" s="5">
         <v>0</v>
       </c>
       <c r="E215" s="2">
+        <f>E214+D215</f>
         <v>35157.93</v>
       </c>
       <c r="F215" s="0" t="inlineStr">
@@ -4865,10 +5176,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C216" s="2">
+      <c r="C216" s="5">
         <v>0</v>
       </c>
       <c r="E216" s="2">
+        <f>E215+D216</f>
         <v>35157.93</v>
       </c>
       <c r="F216" s="0" t="inlineStr">
@@ -4888,13 +5200,14 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C217" s="2">
+      <c r="C217" s="5">
         <v>1</v>
       </c>
       <c r="D217" s="2">
         <v>-6600.54</v>
       </c>
       <c r="E217" s="2">
+        <f>E216+D217</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -4909,10 +5222,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C218" s="2">
+      <c r="C218" s="5">
         <v>0</v>
       </c>
       <c r="E218" s="2">
+        <f>E217+D218</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -4927,10 +5241,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C219" s="2">
+      <c r="C219" s="5">
         <v>0</v>
       </c>
       <c r="E219" s="2">
+        <f>E218+D219</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -4945,10 +5260,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C220" s="2">
+      <c r="C220" s="5">
         <v>0</v>
       </c>
       <c r="E220" s="2">
+        <f>E219+D220</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -4963,10 +5279,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C221" s="2">
+      <c r="C221" s="5">
         <v>0</v>
       </c>
       <c r="E221" s="2">
+        <f>E220+D221</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -4981,10 +5298,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C222" s="2">
+      <c r="C222" s="5">
         <v>0</v>
       </c>
       <c r="E222" s="2">
+        <f>E221+D222</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -4999,10 +5317,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C223" s="2">
+      <c r="C223" s="5">
         <v>0</v>
       </c>
       <c r="E223" s="2">
+        <f>E222+D223</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -5017,10 +5336,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C224" s="2">
+      <c r="C224" s="5">
         <v>0</v>
       </c>
       <c r="E224" s="2">
+        <f>E223+D224</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -5035,10 +5355,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C225" s="2">
+      <c r="C225" s="5">
         <v>0</v>
       </c>
       <c r="E225" s="2">
+        <f>E224+D225</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -5053,13 +5374,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C226" s="2">
+      <c r="C226" s="5">
         <v>1</v>
       </c>
       <c r="D226" s="2">
         <v>0.69</v>
       </c>
       <c r="E226" s="2">
+        <f>E225+D226</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5074,10 +5396,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C227" s="2">
+      <c r="C227" s="5">
         <v>0</v>
       </c>
       <c r="E227" s="2">
+        <f>E226+D227</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5092,10 +5415,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C228" s="2">
+      <c r="C228" s="5">
         <v>0</v>
       </c>
       <c r="E228" s="2">
+        <f>E227+D228</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5110,10 +5434,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C229" s="2">
+      <c r="C229" s="5">
         <v>0</v>
       </c>
       <c r="E229" s="2">
+        <f>E228+D229</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5128,10 +5453,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C230" s="2">
+      <c r="C230" s="5">
         <v>0</v>
       </c>
       <c r="E230" s="2">
+        <f>E229+D230</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5146,10 +5472,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C231" s="2">
+      <c r="C231" s="5">
         <v>0</v>
       </c>
       <c r="E231" s="2">
+        <f>E230+D231</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5164,10 +5491,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C232" s="2">
+      <c r="C232" s="5">
         <v>0</v>
       </c>
       <c r="E232" s="2">
+        <f>E231+D232</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5182,10 +5510,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C233" s="2">
+      <c r="C233" s="5">
         <v>0</v>
       </c>
       <c r="E233" s="2">
+        <f>E232+D233</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5200,10 +5529,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C234" s="2">
+      <c r="C234" s="5">
         <v>0</v>
       </c>
       <c r="E234" s="2">
+        <f>E233+D234</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -5218,13 +5548,14 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C235" s="2">
+      <c r="C235" s="5">
         <v>1</v>
       </c>
       <c r="D235" s="2">
         <v>182.49</v>
       </c>
       <c r="E235" s="2">
+        <f>E234+D235</f>
         <v>28740.57</v>
       </c>
     </row>
@@ -5239,10 +5570,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C236" s="2">
+      <c r="C236" s="5">
         <v>0</v>
       </c>
       <c r="E236" s="2">
+        <f>E235+D236</f>
         <v>28740.57</v>
       </c>
     </row>
@@ -5257,10 +5589,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C237" s="2">
+      <c r="C237" s="5">
         <v>0</v>
       </c>
       <c r="E237" s="2">
+        <f>E236+D237</f>
         <v>28740.57</v>
       </c>
     </row>
@@ -5275,10 +5608,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C238" s="2">
+      <c r="C238" s="5">
         <v>0</v>
       </c>
       <c r="E238" s="2">
+        <f>E237+D238</f>
         <v>28740.57</v>
       </c>
     </row>
@@ -5293,10 +5627,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C239" s="2">
+      <c r="C239" s="5">
         <v>0</v>
       </c>
       <c r="E239" s="2">
+        <f>E238+D239</f>
         <v>28740.57</v>
       </c>
     </row>
@@ -5311,13 +5646,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C240" s="2">
+      <c r="C240" s="5">
         <v>1</v>
       </c>
       <c r="D240" s="2">
         <v>1960.0</v>
       </c>
       <c r="E240" s="2">
+        <f>E239+D240</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -5332,10 +5668,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C241" s="2">
+      <c r="C241" s="5">
         <v>0</v>
       </c>
       <c r="E241" s="2">
+        <f>E240+D241</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -5350,10 +5687,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C242" s="2">
+      <c r="C242" s="5">
         <v>0</v>
       </c>
       <c r="E242" s="2">
+        <f>E241+D242</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -5368,10 +5706,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C243" s="2">
+      <c r="C243" s="5">
         <v>0</v>
       </c>
       <c r="E243" s="2">
+        <f>E242+D243</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -5386,10 +5725,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C244" s="2">
+      <c r="C244" s="5">
         <v>0</v>
       </c>
       <c r="E244" s="2">
+        <f>E243+D244</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -5404,10 +5744,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C245" s="2">
+      <c r="C245" s="5">
         <v>0</v>
       </c>
       <c r="E245" s="2">
+        <f>E244+D245</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -5422,10 +5763,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C246" s="2">
+      <c r="C246" s="5">
         <v>0</v>
       </c>
       <c r="E246" s="2">
+        <f>E245+D246</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -5440,13 +5782,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C247" s="2">
+      <c r="C247" s="5">
         <v>2</v>
       </c>
       <c r="D247" s="2">
         <v>-1139.96</v>
       </c>
       <c r="E247" s="2">
+        <f>E246+D247</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -5461,10 +5804,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C248" s="2">
+      <c r="C248" s="5">
         <v>0</v>
       </c>
       <c r="E248" s="2">
+        <f>E247+D248</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -5479,10 +5823,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C249" s="2">
+      <c r="C249" s="5">
         <v>0</v>
       </c>
       <c r="E249" s="2">
+        <f>E248+D249</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -5497,10 +5842,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C250" s="2">
+      <c r="C250" s="5">
         <v>0</v>
       </c>
       <c r="E250" s="2">
+        <f>E249+D250</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -5515,10 +5861,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C251" s="2">
+      <c r="C251" s="5">
         <v>0</v>
       </c>
       <c r="E251" s="2">
+        <f>E250+D251</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -5533,10 +5880,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C252" s="2">
+      <c r="C252" s="5">
         <v>0</v>
       </c>
       <c r="E252" s="2">
+        <f>E251+D252</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -5551,10 +5899,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C253" s="2">
+      <c r="C253" s="5">
         <v>0</v>
       </c>
       <c r="E253" s="2">
+        <f>E252+D253</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -5569,13 +5918,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C254" s="2">
+      <c r="C254" s="5">
         <v>1</v>
       </c>
       <c r="D254" s="2">
         <v>2335.0</v>
       </c>
       <c r="E254" s="2">
+        <f>E253+D254</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -5590,10 +5940,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C255" s="2">
+      <c r="C255" s="5">
         <v>0</v>
       </c>
       <c r="E255" s="2">
+        <f>E254+D255</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -5608,10 +5959,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C256" s="2">
+      <c r="C256" s="5">
         <v>0</v>
       </c>
       <c r="E256" s="2">
+        <f>E255+D256</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -5626,10 +5978,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C257" s="2">
+      <c r="C257" s="5">
         <v>0</v>
       </c>
       <c r="E257" s="2">
+        <f>E256+D257</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -5644,10 +5997,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C258" s="2">
+      <c r="C258" s="5">
         <v>0</v>
       </c>
       <c r="E258" s="2">
+        <f>E257+D258</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -5662,10 +6016,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C259" s="2">
+      <c r="C259" s="5">
         <v>0</v>
       </c>
       <c r="E259" s="2">
+        <f>E258+D259</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -5680,10 +6035,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C260" s="2">
+      <c r="C260" s="5">
         <v>0</v>
       </c>
       <c r="E260" s="2">
+        <f>E259+D260</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -5698,13 +6054,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C261" s="2">
+      <c r="C261" s="5">
         <v>1</v>
       </c>
       <c r="D261" s="2">
         <v>2215.0</v>
       </c>
       <c r="E261" s="2">
+        <f>E260+D261</f>
         <v>34110.61</v>
       </c>
     </row>
@@ -5719,10 +6076,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C262" s="2">
+      <c r="C262" s="5">
         <v>0</v>
       </c>
       <c r="E262" s="2">
+        <f>E261+D262</f>
         <v>34110.61</v>
       </c>
     </row>
@@ -5737,10 +6095,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C263" s="2">
+      <c r="C263" s="5">
         <v>0</v>
       </c>
       <c r="E263" s="2">
+        <f>E262+D263</f>
         <v>34110.61</v>
       </c>
     </row>
@@ -5755,10 +6114,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C264" s="2">
+      <c r="C264" s="5">
         <v>0</v>
       </c>
       <c r="E264" s="2">
+        <f>E263+D264</f>
         <v>34110.61</v>
       </c>
     </row>
@@ -5773,10 +6133,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C265" s="2">
+      <c r="C265" s="5">
         <v>0</v>
       </c>
       <c r="E265" s="2">
+        <f>E264+D265</f>
         <v>34110.61</v>
       </c>
     </row>
@@ -5791,13 +6152,14 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C266" s="2">
+      <c r="C266" s="5">
         <v>1</v>
       </c>
       <c r="D266" s="2">
         <v>138.02</v>
       </c>
       <c r="E266" s="2">
+        <f>E265+D266</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5812,10 +6174,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C267" s="2">
+      <c r="C267" s="5">
         <v>0</v>
       </c>
       <c r="E267" s="2">
+        <f>E266+D267</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5830,10 +6193,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C268" s="2">
+      <c r="C268" s="5">
         <v>0</v>
       </c>
       <c r="E268" s="2">
+        <f>E267+D268</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5848,10 +6212,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C269" s="2">
+      <c r="C269" s="5">
         <v>0</v>
       </c>
       <c r="E269" s="2">
+        <f>E268+D269</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5866,10 +6231,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C270" s="2">
+      <c r="C270" s="5">
         <v>0</v>
       </c>
       <c r="E270" s="2">
+        <f>E269+D270</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5884,10 +6250,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C271" s="2">
+      <c r="C271" s="5">
         <v>0</v>
       </c>
       <c r="E271" s="2">
+        <f>E270+D271</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5902,10 +6269,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C272" s="2">
+      <c r="C272" s="5">
         <v>0</v>
       </c>
       <c r="E272" s="2">
+        <f>E271+D272</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5920,10 +6288,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C273" s="2">
+      <c r="C273" s="5">
         <v>0</v>
       </c>
       <c r="E273" s="2">
+        <f>E272+D273</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5938,10 +6307,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C274" s="2">
+      <c r="C274" s="5">
         <v>0</v>
       </c>
       <c r="E274" s="2">
+        <f>E273+D274</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5956,10 +6326,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C275" s="2">
+      <c r="C275" s="5">
         <v>0</v>
       </c>
       <c r="E275" s="2">
+        <f>E274+D275</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5974,10 +6345,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C276" s="2">
+      <c r="C276" s="5">
         <v>0</v>
       </c>
       <c r="E276" s="2">
+        <f>E275+D276</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -5992,13 +6364,14 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C277" s="2">
+      <c r="C277" s="5">
         <v>1</v>
       </c>
       <c r="D277" s="2">
         <v>-3774.6</v>
       </c>
       <c r="E277" s="2">
+        <f>E276+D277</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6013,10 +6386,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C278" s="2">
+      <c r="C278" s="5">
         <v>0</v>
       </c>
       <c r="E278" s="2">
+        <f>E277+D278</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6031,10 +6405,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C279" s="2">
+      <c r="C279" s="5">
         <v>0</v>
       </c>
       <c r="E279" s="2">
+        <f>E278+D279</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6049,10 +6424,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C280" s="2">
+      <c r="C280" s="5">
         <v>0</v>
       </c>
       <c r="E280" s="2">
+        <f>E279+D280</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6067,10 +6443,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C281" s="2">
+      <c r="C281" s="5">
         <v>0</v>
       </c>
       <c r="E281" s="2">
+        <f>E280+D281</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6085,10 +6462,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C282" s="2">
+      <c r="C282" s="5">
         <v>0</v>
       </c>
       <c r="E282" s="2">
+        <f>E281+D282</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6103,10 +6481,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C283" s="2">
+      <c r="C283" s="5">
         <v>0</v>
       </c>
       <c r="E283" s="2">
+        <f>E282+D283</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6121,10 +6500,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C284" s="2">
+      <c r="C284" s="5">
         <v>0</v>
       </c>
       <c r="E284" s="2">
+        <f>E283+D284</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6139,10 +6519,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C285" s="2">
+      <c r="C285" s="5">
         <v>0</v>
       </c>
       <c r="E285" s="2">
+        <f>E284+D285</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6157,10 +6538,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C286" s="2">
+      <c r="C286" s="5">
         <v>0</v>
       </c>
       <c r="E286" s="2">
+        <f>E285+D286</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6175,10 +6557,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C287" s="2">
+      <c r="C287" s="5">
         <v>0</v>
       </c>
       <c r="E287" s="2">
+        <f>E286+D287</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6193,10 +6576,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C288" s="2">
+      <c r="C288" s="5">
         <v>0</v>
       </c>
       <c r="E288" s="2">
+        <f>E287+D288</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6211,10 +6595,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C289" s="2">
+      <c r="C289" s="5">
         <v>0</v>
       </c>
       <c r="E289" s="2">
+        <f>E288+D289</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6229,10 +6614,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C290" s="2">
+      <c r="C290" s="5">
         <v>0</v>
       </c>
       <c r="E290" s="2">
+        <f>E289+D290</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6247,10 +6633,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C291" s="2">
+      <c r="C291" s="5">
         <v>0</v>
       </c>
       <c r="E291" s="2">
+        <f>E290+D291</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6265,10 +6652,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C292" s="2">
+      <c r="C292" s="5">
         <v>0</v>
       </c>
       <c r="E292" s="2">
+        <f>E291+D292</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6283,10 +6671,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C293" s="2">
+      <c r="C293" s="5">
         <v>0</v>
       </c>
       <c r="E293" s="2">
+        <f>E292+D293</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6301,10 +6690,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C294" s="2">
+      <c r="C294" s="5">
         <v>0</v>
       </c>
       <c r="E294" s="2">
+        <f>E293+D294</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -6319,13 +6709,14 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C295" s="2">
+      <c r="C295" s="5">
         <v>1</v>
       </c>
       <c r="D295" s="2">
         <v>141.39</v>
       </c>
       <c r="E295" s="2">
+        <f>E294+D295</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6340,10 +6731,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C296" s="2">
+      <c r="C296" s="5">
         <v>0</v>
       </c>
       <c r="E296" s="2">
+        <f>E295+D296</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6358,10 +6750,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C297" s="2">
+      <c r="C297" s="5">
         <v>0</v>
       </c>
       <c r="E297" s="2">
+        <f>E296+D297</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6376,10 +6769,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C298" s="2">
+      <c r="C298" s="5">
         <v>0</v>
       </c>
       <c r="E298" s="2">
+        <f>E297+D298</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6394,10 +6788,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C299" s="2">
+      <c r="C299" s="5">
         <v>0</v>
       </c>
       <c r="E299" s="2">
+        <f>E298+D299</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6412,10 +6807,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C300" s="2">
+      <c r="C300" s="5">
         <v>0</v>
       </c>
       <c r="E300" s="2">
+        <f>E299+D300</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6430,10 +6826,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C301" s="2">
+      <c r="C301" s="5">
         <v>0</v>
       </c>
       <c r="E301" s="2">
+        <f>E300+D301</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6448,10 +6845,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C302" s="2">
+      <c r="C302" s="5">
         <v>0</v>
       </c>
       <c r="E302" s="2">
+        <f>E301+D302</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6466,10 +6864,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C303" s="2">
+      <c r="C303" s="5">
         <v>0</v>
       </c>
       <c r="E303" s="2">
+        <f>E302+D303</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6484,10 +6883,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C304" s="2">
+      <c r="C304" s="5">
         <v>0</v>
       </c>
       <c r="E304" s="2">
+        <f>E303+D304</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6502,10 +6902,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C305" s="2">
+      <c r="C305" s="5">
         <v>0</v>
       </c>
       <c r="E305" s="2">
+        <f>E304+D305</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6520,10 +6921,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C306" s="2">
+      <c r="C306" s="5">
         <v>0</v>
       </c>
       <c r="E306" s="2">
+        <f>E305+D306</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6538,10 +6940,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C307" s="2">
+      <c r="C307" s="5">
         <v>0</v>
       </c>
       <c r="E307" s="2">
+        <f>E306+D307</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6556,10 +6959,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C308" s="2">
+      <c r="C308" s="5">
         <v>0</v>
       </c>
       <c r="E308" s="2">
+        <f>E307+D308</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6574,10 +6978,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C309" s="2">
+      <c r="C309" s="5">
         <v>0</v>
       </c>
       <c r="E309" s="2">
+        <f>E308+D309</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6592,10 +6997,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C310" s="2">
+      <c r="C310" s="5">
         <v>0</v>
       </c>
       <c r="E310" s="2">
+        <f>E309+D310</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6610,10 +7016,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C311" s="2">
+      <c r="C311" s="5">
         <v>0</v>
       </c>
       <c r="E311" s="2">
+        <f>E310+D311</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6628,10 +7035,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C312" s="2">
+      <c r="C312" s="5">
         <v>0</v>
       </c>
       <c r="E312" s="2">
+        <f>E311+D312</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6646,10 +7054,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C313" s="2">
+      <c r="C313" s="5">
         <v>0</v>
       </c>
       <c r="E313" s="2">
+        <f>E312+D313</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6664,10 +7073,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C314" s="2">
+      <c r="C314" s="5">
         <v>0</v>
       </c>
       <c r="E314" s="2">
+        <f>E313+D314</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6682,10 +7092,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C315" s="2">
+      <c r="C315" s="5">
         <v>0</v>
       </c>
       <c r="E315" s="2">
+        <f>E314+D315</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6700,10 +7111,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C316" s="2">
+      <c r="C316" s="5">
         <v>0</v>
       </c>
       <c r="E316" s="2">
+        <f>E315+D316</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -6718,13 +7130,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C317" s="2">
+      <c r="C317" s="5">
         <v>2</v>
       </c>
       <c r="D317" s="2">
         <v>-79.69</v>
       </c>
       <c r="E317" s="2">
+        <f>E316+D317</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6739,10 +7152,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C318" s="2">
+      <c r="C318" s="5">
         <v>0</v>
       </c>
       <c r="E318" s="2">
+        <f>E317+D318</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6757,10 +7171,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C319" s="2">
+      <c r="C319" s="5">
         <v>0</v>
       </c>
       <c r="E319" s="2">
+        <f>E318+D319</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6775,10 +7190,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C320" s="2">
+      <c r="C320" s="5">
         <v>0</v>
       </c>
       <c r="E320" s="2">
+        <f>E319+D320</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6793,10 +7209,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C321" s="2">
+      <c r="C321" s="5">
         <v>0</v>
       </c>
       <c r="E321" s="2">
+        <f>E320+D321</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6811,10 +7228,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C322" s="2">
+      <c r="C322" s="5">
         <v>0</v>
       </c>
       <c r="E322" s="2">
+        <f>E321+D322</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6829,10 +7247,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C323" s="2">
+      <c r="C323" s="5">
         <v>0</v>
       </c>
       <c r="E323" s="2">
+        <f>E322+D323</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6847,10 +7266,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C324" s="2">
+      <c r="C324" s="5">
         <v>0</v>
       </c>
       <c r="E324" s="2">
+        <f>E323+D324</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6865,10 +7285,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C325" s="2">
+      <c r="C325" s="5">
         <v>0</v>
       </c>
       <c r="E325" s="2">
+        <f>E324+D325</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -6883,13 +7304,14 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C326" s="2">
+      <c r="C326" s="5">
         <v>1</v>
       </c>
       <c r="D326" s="2">
         <v>177.84</v>
       </c>
       <c r="E326" s="2">
+        <f>E325+D326</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -6904,10 +7326,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C327" s="2">
+      <c r="C327" s="5">
         <v>0</v>
       </c>
       <c r="E327" s="2">
+        <f>E326+D327</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -6922,10 +7345,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C328" s="2">
+      <c r="C328" s="5">
         <v>0</v>
       </c>
       <c r="E328" s="2">
+        <f>E327+D328</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -6940,10 +7364,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C329" s="2">
+      <c r="C329" s="5">
         <v>0</v>
       </c>
       <c r="E329" s="2">
+        <f>E328+D329</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -6958,10 +7383,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C330" s="2">
+      <c r="C330" s="5">
         <v>0</v>
       </c>
       <c r="E330" s="2">
+        <f>E329+D330</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -6976,10 +7402,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C331" s="2">
+      <c r="C331" s="5">
         <v>0</v>
       </c>
       <c r="E331" s="2">
+        <f>E330+D331</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -6994,10 +7421,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C332" s="2">
+      <c r="C332" s="5">
         <v>0</v>
       </c>
       <c r="E332" s="2">
+        <f>E331+D332</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -7012,10 +7440,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C333" s="2">
+      <c r="C333" s="5">
         <v>0</v>
       </c>
       <c r="E333" s="2">
+        <f>E332+D333</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -7030,10 +7459,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C334" s="2">
+      <c r="C334" s="5">
         <v>0</v>
       </c>
       <c r="E334" s="2">
+        <f>E333+D334</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -7048,10 +7478,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C335" s="2">
+      <c r="C335" s="5">
         <v>0</v>
       </c>
       <c r="E335" s="2">
+        <f>E334+D335</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -7066,10 +7497,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C336" s="2">
+      <c r="C336" s="5">
         <v>0</v>
       </c>
       <c r="E336" s="2">
+        <f>E335+D336</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -7084,13 +7516,14 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C337" s="2">
+      <c r="C337" s="5">
         <v>1</v>
       </c>
       <c r="D337" s="2">
         <v>-93.06</v>
       </c>
       <c r="E337" s="2">
+        <f>E336+D337</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7105,10 +7538,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C338" s="2">
+      <c r="C338" s="5">
         <v>0</v>
       </c>
       <c r="E338" s="2">
+        <f>E337+D338</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7123,10 +7557,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C339" s="2">
+      <c r="C339" s="5">
         <v>0</v>
       </c>
       <c r="E339" s="2">
+        <f>E338+D339</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7141,10 +7576,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C340" s="2">
+      <c r="C340" s="5">
         <v>0</v>
       </c>
       <c r="E340" s="2">
+        <f>E339+D340</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7159,10 +7595,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C341" s="2">
+      <c r="C341" s="5">
         <v>0</v>
       </c>
       <c r="E341" s="2">
+        <f>E340+D341</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7177,10 +7614,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C342" s="2">
+      <c r="C342" s="5">
         <v>0</v>
       </c>
       <c r="E342" s="2">
+        <f>E341+D342</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7195,10 +7633,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C343" s="2">
+      <c r="C343" s="5">
         <v>0</v>
       </c>
       <c r="E343" s="2">
+        <f>E342+D343</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7213,10 +7652,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C344" s="2">
+      <c r="C344" s="5">
         <v>0</v>
       </c>
       <c r="E344" s="2">
+        <f>E343+D344</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7231,10 +7671,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C345" s="2">
+      <c r="C345" s="5">
         <v>0</v>
       </c>
       <c r="E345" s="2">
+        <f>E344+D345</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7249,10 +7690,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C346" s="2">
+      <c r="C346" s="5">
         <v>0</v>
       </c>
       <c r="E346" s="2">
+        <f>E345+D346</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7267,10 +7709,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C347" s="2">
+      <c r="C347" s="5">
         <v>0</v>
       </c>
       <c r="E347" s="2">
+        <f>E346+D347</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7285,10 +7728,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C348" s="2">
+      <c r="C348" s="5">
         <v>0</v>
       </c>
       <c r="E348" s="2">
+        <f>E347+D348</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7303,10 +7747,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C349" s="2">
+      <c r="C349" s="5">
         <v>0</v>
       </c>
       <c r="E349" s="2">
+        <f>E348+D349</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7321,10 +7766,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C350" s="2">
+      <c r="C350" s="5">
         <v>0</v>
       </c>
       <c r="E350" s="2">
+        <f>E349+D350</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7339,10 +7785,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C351" s="2">
+      <c r="C351" s="5">
         <v>0</v>
       </c>
       <c r="E351" s="2">
+        <f>E350+D351</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7357,10 +7804,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C352" s="2">
+      <c r="C352" s="5">
         <v>0</v>
       </c>
       <c r="E352" s="2">
+        <f>E351+D352</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7375,10 +7823,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C353" s="2">
+      <c r="C353" s="5">
         <v>0</v>
       </c>
       <c r="E353" s="2">
+        <f>E352+D353</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7393,10 +7842,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C354" s="2">
+      <c r="C354" s="5">
         <v>0</v>
       </c>
       <c r="E354" s="2">
+        <f>E353+D354</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7411,10 +7861,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C355" s="2">
+      <c r="C355" s="5">
         <v>0</v>
       </c>
       <c r="E355" s="2">
+        <f>E354+D355</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7429,10 +7880,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C356" s="2">
+      <c r="C356" s="5">
         <v>0</v>
       </c>
       <c r="E356" s="2">
+        <f>E355+D356</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7447,10 +7899,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C357" s="2">
+      <c r="C357" s="5">
         <v>0</v>
       </c>
       <c r="E357" s="2">
+        <f>E356+D357</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7465,10 +7918,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C358" s="2">
+      <c r="C358" s="5">
         <v>0</v>
       </c>
       <c r="E358" s="2">
+        <f>E357+D358</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7483,10 +7937,11 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C359" s="2">
+      <c r="C359" s="5">
         <v>0</v>
       </c>
       <c r="E359" s="2">
+        <f>E358+D359</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7501,10 +7956,11 @@
           <t xml:space="preserve">Thu</t>
         </is>
       </c>
-      <c r="C360" s="2">
+      <c r="C360" s="5">
         <v>0</v>
       </c>
       <c r="E360" s="2">
+        <f>E359+D360</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7519,10 +7975,11 @@
           <t xml:space="preserve">Fri</t>
         </is>
       </c>
-      <c r="C361" s="2">
+      <c r="C361" s="5">
         <v>0</v>
       </c>
       <c r="E361" s="2">
+        <f>E360+D361</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7537,10 +7994,11 @@
           <t xml:space="preserve">Sat</t>
         </is>
       </c>
-      <c r="C362" s="2">
+      <c r="C362" s="5">
         <v>0</v>
       </c>
       <c r="E362" s="2">
+        <f>E361+D362</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7555,10 +8013,11 @@
           <t xml:space="preserve">Sun</t>
         </is>
       </c>
-      <c r="C363" s="2">
+      <c r="C363" s="5">
         <v>0</v>
       </c>
       <c r="E363" s="2">
+        <f>E362+D363</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7573,10 +8032,11 @@
           <t xml:space="preserve">Mon</t>
         </is>
       </c>
-      <c r="C364" s="2">
+      <c r="C364" s="5">
         <v>0</v>
       </c>
       <c r="E364" s="2">
+        <f>E363+D364</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7591,10 +8051,11 @@
           <t xml:space="preserve">Tue</t>
         </is>
       </c>
-      <c r="C365" s="2">
+      <c r="C365" s="5">
         <v>0</v>
       </c>
       <c r="E365" s="2">
+        <f>E364+D365</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -7609,13 +8070,14 @@
           <t xml:space="preserve">Wed</t>
         </is>
       </c>
-      <c r="C366" s="2">
+      <c r="C366" s="5">
         <v>1</v>
       </c>
       <c r="D366" s="2">
         <v>1500.0</v>
       </c>
       <c r="E366" s="2">
+        <f>E365+D366</f>
         <v>32120.51</v>
       </c>
     </row>
@@ -7703,6 +8165,7 @@
         </is>
       </c>
       <c r="B2" s="2">
+        <f>Summary!D2</f>
         <v>11053.84</v>
       </c>
       <c r="C2" s="2">
@@ -7712,20 +8175,22 @@
         <v>0.0</v>
       </c>
       <c r="E2" s="2">
+        <f>C2+D2</f>
         <v>2250.0</v>
       </c>
       <c r="F2" s="2">
+        <f>B2+E2</f>
         <v>13303.84</v>
       </c>
       <c r="G2" s="2">
         <v>13303.84</v>
       </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H2" s="0" t="str">
+        <f>IF(F2=G2,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I2" s="2">
+        <f>MAX(Daily!E2:E32)</f>
         <v>13303.84</v>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -7733,7 +8198,7 @@
           <t xml:space="preserve">2025-01-07</t>
         </is>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="5">
         <v>1</v>
       </c>
     </row>
@@ -7744,6 +8209,7 @@
         </is>
       </c>
       <c r="B3" s="2">
+        <f>F2</f>
         <v>13303.84</v>
       </c>
       <c r="C3" s="2">
@@ -7753,20 +8219,22 @@
         <v>0.0</v>
       </c>
       <c r="E3" s="2">
+        <f>C3+D3</f>
         <v>0.0</v>
       </c>
       <c r="F3" s="2">
+        <f>B3+E3</f>
         <v>13303.84</v>
       </c>
       <c r="G3" s="2">
         <v>13303.84</v>
       </c>
-      <c r="H3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H3" s="0" t="str">
+        <f>IF(F3=G3,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I3" s="2">
+        <f>MAX(Daily!E33:E60)</f>
         <v>13303.84</v>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -7774,7 +8242,7 @@
           <t xml:space="preserve">2025-02-01</t>
         </is>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7785,6 +8253,7 @@
         </is>
       </c>
       <c r="B4" s="2">
+        <f>F3</f>
         <v>13303.84</v>
       </c>
       <c r="C4" s="2">
@@ -7794,20 +8263,22 @@
         <v>-106.58</v>
       </c>
       <c r="E4" s="2">
+        <f>C4+D4</f>
         <v>3681.56</v>
       </c>
       <c r="F4" s="2">
+        <f>B4+E4</f>
         <v>16985.4</v>
       </c>
       <c r="G4" s="2">
         <v>16985.4</v>
       </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H4" s="0" t="str">
+        <f>IF(F4=G4,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I4" s="2">
+        <f>MAX(Daily!E61:E91)</f>
         <v>16985.4</v>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -7815,7 +8286,7 @@
           <t xml:space="preserve">2025-03-26</t>
         </is>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="5">
         <v>3</v>
       </c>
     </row>
@@ -7826,6 +8297,7 @@
         </is>
       </c>
       <c r="B5" s="2">
+        <f>F4</f>
         <v>16985.4</v>
       </c>
       <c r="C5" s="2">
@@ -7835,20 +8307,22 @@
         <v>-1.08</v>
       </c>
       <c r="E5" s="2">
+        <f>C5+D5</f>
         <v>12010.8</v>
       </c>
       <c r="F5" s="2">
+        <f>B5+E5</f>
         <v>28996.2</v>
       </c>
       <c r="G5" s="2">
         <v>28996.2</v>
       </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H5" s="0" t="str">
+        <f>IF(F5=G5,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I5" s="2">
+        <f>MAX(Daily!E92:E121)</f>
         <v>28997.24</v>
       </c>
       <c r="J5" s="0" t="inlineStr">
@@ -7856,7 +8330,7 @@
           <t xml:space="preserve">2025-04-07</t>
         </is>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="5">
         <v>5</v>
       </c>
     </row>
@@ -7867,6 +8341,7 @@
         </is>
       </c>
       <c r="B6" s="2">
+        <f>F5</f>
         <v>28996.2</v>
       </c>
       <c r="C6" s="2">
@@ -7876,20 +8351,22 @@
         <v>0.0</v>
       </c>
       <c r="E6" s="2">
+        <f>C6+D6</f>
         <v>0.0</v>
       </c>
       <c r="F6" s="2">
+        <f>B6+E6</f>
         <v>28996.2</v>
       </c>
       <c r="G6" s="2">
         <v>28996.2</v>
       </c>
-      <c r="H6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H6" s="0" t="str">
+        <f>IF(F6=G6,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I6" s="2">
+        <f>MAX(Daily!E122:E152)</f>
         <v>28996.2</v>
       </c>
       <c r="J6" s="0" t="inlineStr">
@@ -7897,7 +8374,7 @@
           <t xml:space="preserve">2025-05-01</t>
         </is>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7908,6 +8385,7 @@
         </is>
       </c>
       <c r="B7" s="2">
+        <f>F6</f>
         <v>28996.2</v>
       </c>
       <c r="C7" s="2">
@@ -7917,20 +8395,22 @@
         <v>-6.44</v>
       </c>
       <c r="E7" s="2">
+        <f>C7+D7</f>
         <v>320.56</v>
       </c>
       <c r="F7" s="2">
+        <f>B7+E7</f>
         <v>29316.76</v>
       </c>
       <c r="G7" s="2">
         <v>29316.76</v>
       </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H7" s="0" t="str">
+        <f>IF(F7=G7,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I7" s="2">
+        <f>MAX(Daily!E153:E182)</f>
         <v>29323.2</v>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -7938,7 +8418,7 @@
           <t xml:space="preserve">2025-06-27</t>
         </is>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="5">
         <v>2</v>
       </c>
     </row>
@@ -7949,6 +8429,7 @@
         </is>
       </c>
       <c r="B8" s="2">
+        <f>F7</f>
         <v>29316.76</v>
       </c>
       <c r="C8" s="2">
@@ -7958,20 +8439,22 @@
         <v>-2640.22</v>
       </c>
       <c r="E8" s="2">
+        <f>C8+D8</f>
         <v>5841.17</v>
       </c>
       <c r="F8" s="2">
+        <f>B8+E8</f>
         <v>35157.93</v>
       </c>
       <c r="G8" s="2">
         <v>35157.93</v>
       </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H8" s="0" t="str">
+        <f>IF(F8=G8,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I8" s="2">
+        <f>MAX(Daily!E183:E213)</f>
         <v>35157.93</v>
       </c>
       <c r="J8" s="0" t="inlineStr">
@@ -7979,7 +8462,7 @@
           <t xml:space="preserve">2025-07-31</t>
         </is>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="5">
         <v>6</v>
       </c>
     </row>
@@ -7990,6 +8473,7 @@
         </is>
       </c>
       <c r="B9" s="2">
+        <f>F8</f>
         <v>35157.93</v>
       </c>
       <c r="C9" s="2">
@@ -7999,20 +8483,22 @@
         <v>-6600.54</v>
       </c>
       <c r="E9" s="2">
+        <f>C9+D9</f>
         <v>-4457.36</v>
       </c>
       <c r="F9" s="2">
+        <f>B9+E9</f>
         <v>30700.57</v>
       </c>
       <c r="G9" s="2">
         <v>30700.57</v>
       </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H9" s="0" t="str">
+        <f>IF(F9=G9,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I9" s="2">
+        <f>MAX(Daily!E214:E244)</f>
         <v>35157.93</v>
       </c>
       <c r="J9" s="0" t="inlineStr">
@@ -8020,7 +8506,7 @@
           <t xml:space="preserve">2025-08-01</t>
         </is>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="5">
         <v>4</v>
       </c>
     </row>
@@ -8031,6 +8517,7 @@
         </is>
       </c>
       <c r="B10" s="2">
+        <f>F9</f>
         <v>30700.57</v>
       </c>
       <c r="C10" s="2">
@@ -8040,20 +8527,22 @@
         <v>-2359.96</v>
       </c>
       <c r="E10" s="2">
+        <f>C10+D10</f>
         <v>3548.06</v>
       </c>
       <c r="F10" s="2">
+        <f>B10+E10</f>
         <v>34248.63</v>
       </c>
       <c r="G10" s="2">
         <v>34248.63</v>
       </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H10" s="0" t="str">
+        <f>IF(F10=G10,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I10" s="2">
+        <f>MAX(Daily!E245:E274)</f>
         <v>34248.63</v>
       </c>
       <c r="J10" s="0" t="inlineStr">
@@ -8061,7 +8550,7 @@
           <t xml:space="preserve">2025-09-22</t>
         </is>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="5">
         <v>5</v>
       </c>
     </row>
@@ -8072,6 +8561,7 @@
         </is>
       </c>
       <c r="B11" s="2">
+        <f>F10</f>
         <v>34248.63</v>
       </c>
       <c r="C11" s="2">
@@ -8081,20 +8571,22 @@
         <v>-3774.6</v>
       </c>
       <c r="E11" s="2">
+        <f>C11+D11</f>
         <v>-3633.21</v>
       </c>
       <c r="F11" s="2">
+        <f>B11+E11</f>
         <v>30615.42</v>
       </c>
       <c r="G11" s="2">
         <v>30615.42</v>
       </c>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H11" s="0" t="str">
+        <f>IF(F11=G11,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I11" s="2">
+        <f>MAX(Daily!E275:E305)</f>
         <v>34248.63</v>
       </c>
       <c r="J11" s="0" t="inlineStr">
@@ -8102,7 +8594,7 @@
           <t xml:space="preserve">2025-10-01</t>
         </is>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="5">
         <v>2</v>
       </c>
     </row>
@@ -8113,6 +8605,7 @@
         </is>
       </c>
       <c r="B12" s="2">
+        <f>F11</f>
         <v>30615.42</v>
       </c>
       <c r="C12" s="2">
@@ -8122,20 +8615,22 @@
         <v>-80.9</v>
       </c>
       <c r="E12" s="2">
+        <f>C12+D12</f>
         <v>98.15</v>
       </c>
       <c r="F12" s="2">
+        <f>B12+E12</f>
         <v>30713.57</v>
       </c>
       <c r="G12" s="2">
         <v>30713.57</v>
       </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H12" s="0" t="str">
+        <f>IF(F12=G12,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I12" s="2">
+        <f>MAX(Daily!E306:E335)</f>
         <v>30713.57</v>
       </c>
       <c r="J12" s="0" t="inlineStr">
@@ -8143,7 +8638,7 @@
           <t xml:space="preserve">2025-11-21</t>
         </is>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="5">
         <v>3</v>
       </c>
     </row>
@@ -8154,6 +8649,7 @@
         </is>
       </c>
       <c r="B13" s="2">
+        <f>F12</f>
         <v>30713.57</v>
       </c>
       <c r="C13" s="2">
@@ -8163,20 +8659,22 @@
         <v>-93.06</v>
       </c>
       <c r="E13" s="2">
+        <f>C13+D13</f>
         <v>1406.94</v>
       </c>
       <c r="F13" s="2">
+        <f>B13+E13</f>
         <v>32120.51</v>
       </c>
       <c r="G13" s="2">
         <v>32120.51</v>
       </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H13" s="0" t="str">
+        <f>IF(F13=G13,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I13" s="2">
+        <f>MAX(Daily!E336:E366)</f>
         <v>32120.51</v>
       </c>
       <c r="J13" s="0" t="inlineStr">
@@ -8184,7 +8682,7 @@
           <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="5">
         <v>2</v>
       </c>
     </row>
@@ -8195,29 +8693,35 @@
         </is>
       </c>
       <c r="B14" s="3">
+        <f>Summary!D2</f>
         <v>11053.84</v>
       </c>
       <c r="C14" s="3">
+        <f>SUM(C2:C13)</f>
         <v>36730.05</v>
       </c>
       <c r="D14" s="3">
+        <f>SUM(D2:D13)</f>
         <v>-15663.38</v>
       </c>
       <c r="E14" s="3">
+        <f>C14+D14</f>
         <v>21066.67</v>
       </c>
       <c r="F14" s="3">
+        <f>B14+E14</f>
         <v>32120.51</v>
       </c>
       <c r="G14" s="3">
+        <f>F13</f>
         <v>32120.51</v>
       </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MATCH</t>
-        </is>
+      <c r="H14" s="1" t="str">
+        <f>IF(F14=G14,"MATCH","MISMATCH")</f>
+        <v>MATCH</v>
       </c>
       <c r="I14" s="3">
+        <f>MAX(Daily!E2:E366)</f>
         <v>35157.93</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
@@ -8225,7 +8729,8 @@
           <t xml:space="preserve">2025-07-31</t>
         </is>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="6">
+        <f>SUM(K2:K13)</f>
         <v>33</v>
       </c>
     </row>
@@ -8312,6 +8817,7 @@
         <v>2250.0</v>
       </c>
       <c r="G2" s="2">
+        <f>Summary!D2+F2</f>
         <v>13303.84</v>
       </c>
     </row>
@@ -8333,18 +8839,19 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice No. 5198439717</t>
+          <t xml:space="preserve">Invoice No. 5198439717 · your label: Google CL</t>
         </is>
       </c>
       <c r="F3" s="2">
         <v>-16.58</v>
       </c>
       <c r="G3" s="2">
+        <f>G2+F3</f>
         <v>13287.26</v>
       </c>
     </row>
@@ -8366,18 +8873,19 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raunac CA</t>
+          <t xml:space="preserve">Books &amp; Counts LLC</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITR GCALIT LLC Filed by RAUNAC</t>
+          <t xml:space="preserve">ITR GCALIT LLC Filed by RAUNAC · your label: Raunac CA</t>
         </is>
       </c>
       <c r="F4" s="2">
         <v>-90.0</v>
       </c>
       <c r="G4" s="2">
+        <f>G3+F4</f>
         <v>13197.26</v>
       </c>
     </row>
@@ -8411,6 +8919,7 @@
         <v>3788.14</v>
       </c>
       <c r="G5" s="2">
+        <f>G4+F5</f>
         <v>16985.4</v>
       </c>
     </row>
@@ -8444,6 +8953,7 @@
         <v>8548.04</v>
       </c>
       <c r="G6" s="2">
+        <f>G5+F6</f>
         <v>25533.44</v>
       </c>
     </row>
@@ -8477,6 +8987,7 @@
         <v>1340.0</v>
       </c>
       <c r="G7" s="2">
+        <f>G6+F7</f>
         <v>26873.44</v>
       </c>
     </row>
@@ -8510,6 +9021,7 @@
         <v>2123.8</v>
       </c>
       <c r="G8" s="2">
+        <f>G7+F8</f>
         <v>28997.24</v>
       </c>
     </row>
@@ -8531,18 +9043,19 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send Money transaction initiated on Mercury</t>
+          <t xml:space="preserve">Send Money transaction initiated on Mercury · your label: Google CL</t>
         </is>
       </c>
       <c r="F9" s="2">
         <v>-1.08</v>
       </c>
       <c r="G9" s="2">
+        <f>G8+F9</f>
         <v>28996.16</v>
       </c>
     </row>
@@ -8576,6 +9089,7 @@
         <v>0.04</v>
       </c>
       <c r="G10" s="2">
+        <f>G9+F10</f>
         <v>28996.2</v>
       </c>
     </row>
@@ -8609,6 +9123,7 @@
         <v>327.0</v>
       </c>
       <c r="G11" s="2">
+        <f>G10+F11</f>
         <v>29323.2</v>
       </c>
     </row>
@@ -8630,18 +9145,19 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice number: 5276703039; Invoice Number - 5276703039 Invoice Date - May 31, 2025 Billing ID - 8327-3971-0682 Account ID  - 405-199-0952</t>
+          <t xml:space="preserve">Invoice number: 5276703039; Invoice Number - 5276703039 Invoice Date - May 31, 2025 Billing ID - 8327-3971-0682 Account ID  - 405-199-0952 · your label: Google CL</t>
         </is>
       </c>
       <c r="F12" s="2">
         <v>-6.44</v>
       </c>
       <c r="G12" s="2">
+        <f>G11+F12</f>
         <v>29316.76</v>
       </c>
     </row>
@@ -8663,18 +9179,19 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice Payment 5300675820; Invoice Number - 5300675820 Invoice Date - June 30, 2025 Billing ID - 8327-3971-0682 Account ID  - 405-199-0952</t>
+          <t xml:space="preserve">Invoice Payment 5300675820; Invoice Number - 5300675820 Invoice Date - June 30, 2025 Billing ID - 8327-3971-0682 Account ID  - 405-199-0952 · your label: Google CL</t>
         </is>
       </c>
       <c r="F13" s="2">
         <v>-2398.97</v>
       </c>
       <c r="G13" s="2">
+        <f>G12+F13</f>
         <v>26917.79</v>
       </c>
     </row>
@@ -8708,6 +9225,7 @@
         <v>6347.78</v>
       </c>
       <c r="G14" s="2">
+        <f>G13+F14</f>
         <v>33265.57</v>
       </c>
     </row>
@@ -8741,6 +9259,7 @@
         <v>-241.25</v>
       </c>
       <c r="G15" s="2">
+        <f>G14+F15</f>
         <v>33024.32</v>
       </c>
     </row>
@@ -8769,6 +9288,7 @@
         <v>3.61</v>
       </c>
       <c r="G16" s="2">
+        <f>G15+F16</f>
         <v>33027.93</v>
       </c>
     </row>
@@ -8797,6 +9317,7 @@
         <v>1380.0</v>
       </c>
       <c r="G17" s="2">
+        <f>G16+F17</f>
         <v>34407.93</v>
       </c>
     </row>
@@ -8830,6 +9351,7 @@
         <v>750.0</v>
       </c>
       <c r="G18" s="3">
+        <f>G17+F18</f>
         <v>35157.93</v>
       </c>
     </row>
@@ -8851,18 +9373,19 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice number: 5331260440; Invoice Number - 5331260440 Invoice Date - July 31, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT1-4</t>
+          <t xml:space="preserve">Invoice number: 5331260440; Invoice Number - 5331260440 Invoice Date - July 31, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT1-4 · your label: Google CL</t>
         </is>
       </c>
       <c r="F19" s="2">
         <v>-6600.54</v>
       </c>
       <c r="G19" s="2">
+        <f>G18+F19</f>
         <v>28557.39</v>
       </c>
     </row>
@@ -8896,6 +9419,7 @@
         <v>0.69</v>
       </c>
       <c r="G20" s="2">
+        <f>G19+F20</f>
         <v>28558.08</v>
       </c>
     </row>
@@ -8929,6 +9453,7 @@
         <v>182.49</v>
       </c>
       <c r="G21" s="2">
+        <f>G20+F21</f>
         <v>28740.57</v>
       </c>
     </row>
@@ -8957,6 +9482,7 @@
         <v>1960.0</v>
       </c>
       <c r="G22" s="2">
+        <f>G21+F22</f>
         <v>30700.57</v>
       </c>
     </row>
@@ -8985,6 +9511,7 @@
         <v>1220.0</v>
       </c>
       <c r="G23" s="2">
+        <f>G22+F23</f>
         <v>31920.57</v>
       </c>
     </row>
@@ -9006,18 +9533,19 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUG 31,2025 -5353915159; Vendor: Invoice Number - 5353915159 Invoice Date - Aug 31, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT1-6</t>
+          <t xml:space="preserve">AUG 31,2025 -5353915159; Vendor: Invoice Number - 5353915159 Invoice Date - Aug 31, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT1-6 · your label: Google CL</t>
         </is>
       </c>
       <c r="F24" s="2">
         <v>-2359.96</v>
       </c>
       <c r="G24" s="2">
+        <f>G23+F24</f>
         <v>29560.61</v>
       </c>
     </row>
@@ -9046,6 +9574,7 @@
         <v>2335.0</v>
       </c>
       <c r="G25" s="2">
+        <f>G24+F25</f>
         <v>31895.61</v>
       </c>
     </row>
@@ -9074,6 +9603,7 @@
         <v>2215.0</v>
       </c>
       <c r="G26" s="2">
+        <f>G25+F26</f>
         <v>34110.61</v>
       </c>
     </row>
@@ -9107,6 +9637,7 @@
         <v>138.02</v>
       </c>
       <c r="G27" s="2">
+        <f>G26+F27</f>
         <v>34248.63</v>
       </c>
     </row>
@@ -9128,18 +9659,19 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">For 5377217442 Sept; Vendor: Invoice Number - 5377217442 Invoice Date - Sep 30, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT2,3,4,6</t>
+          <t xml:space="preserve">For 5377217442 Sept; Vendor: Invoice Number - 5377217442 Invoice Date - Sep 30, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT2,3,4,6 · your label: Google CL</t>
         </is>
       </c>
       <c r="F28" s="2">
         <v>-3774.6</v>
       </c>
       <c r="G28" s="2">
+        <f>G27+F28</f>
         <v>30474.03</v>
       </c>
     </row>
@@ -9173,6 +9705,7 @@
         <v>141.39</v>
       </c>
       <c r="G29" s="2">
+        <f>G28+F29</f>
         <v>30615.42</v>
       </c>
     </row>
@@ -9206,6 +9739,7 @@
         <v>-80.9</v>
       </c>
       <c r="G30" s="2">
+        <f>G29+F30</f>
         <v>30534.52</v>
       </c>
     </row>
@@ -9234,6 +9768,7 @@
         <v>1.21</v>
       </c>
       <c r="G31" s="2">
+        <f>G30+F31</f>
         <v>30535.73</v>
       </c>
     </row>
@@ -9267,6 +9802,7 @@
         <v>177.84</v>
       </c>
       <c r="G32" s="2">
+        <f>G31+F32</f>
         <v>30713.57</v>
       </c>
     </row>
@@ -9288,18 +9824,19 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google CL</t>
+          <t xml:space="preserve">Google LLC</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">via mercury.com; Vendor: Invoice Number - 5430635554 Invoice Date - Nov 30, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT7</t>
+          <t xml:space="preserve">via mercury.com; Vendor: Invoice Number - 5430635554 Invoice Date - Nov 30, 2025 Billing ID - 8327-3971-0682 Account ID  - GCALIT7 · your label: Google CL</t>
         </is>
       </c>
       <c r="F33" s="2">
         <v>-93.06</v>
       </c>
       <c r="G33" s="2">
+        <f>G32+F33</f>
         <v>30620.51</v>
       </c>
     </row>
@@ -9328,6 +9865,7 @@
         <v>1500.0</v>
       </c>
       <c r="G34" s="2">
+        <f>G33+F34</f>
         <v>32120.51</v>
       </c>
     </row>
@@ -9504,6 +10042,11 @@
           <t xml:space="preserve">TOTAL CARD SPEND</t>
         </is>
       </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchases charged to the card during 2025</t>
+        </is>
+      </c>
       <c r="E8" s="3">
         <v>-322.15</v>
       </c>
@@ -9514,6 +10057,11 @@
           <t xml:space="preserve">TOTAL REFUNDS</t>
         </is>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merchant refunds credited back to the card</t>
+        </is>
+      </c>
       <c r="E9" s="2">
         <v>0.0</v>
       </c>
@@ -9526,7 +10074,7 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mirrors the two 'Sent to card' rows on the bank ledger</t>
+          <t xml:space="preserve">Mirrors the 'Sent to card' rows on the bank ledger</t>
         </is>
       </c>
       <c r="E10" s="2">
@@ -9545,6 +10093,7 @@
         </is>
       </c>
       <c r="E11" s="3">
+        <f>E8+E9+E10</f>
         <v>0.0</v>
       </c>
     </row>
@@ -9557,7 +10106,7 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The credit account was opened on 2025-05-11, after the year began, so nothing could be owed on 1 January</t>
+          <t xml:space="preserve">Account opened 2025-05-11, after the year began, so nothing could be owed on 1 January</t>
         </is>
       </c>
       <c r="E13" s="2">
@@ -9572,7 +10121,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every charge raised in 2025 was paid off, so the cash and accrual views of this year agree. In a year that ends with a balance owed they would not.</t>
+          <t xml:space="preserve">Every 2025 charge was paid off, so cash and accrual agree this year. Point-in-time: the next charge landed days into 2026.</t>
         </is>
       </c>
       <c r="E14" s="2">
@@ -9655,7 +10204,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">A — Statement</t>
+          <t xml:space="preserve">B — Statement</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -9681,7 +10230,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">B — Back-computed</t>
+          <t xml:space="preserve">C — Back-computed</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
@@ -9707,7 +10256,7 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">C — Forward</t>
+          <t xml:space="preserve">D — Forward</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
@@ -9733,7 +10282,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">D — From account opening</t>
+          <t xml:space="preserve">E — From account opening</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -9759,7 +10308,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">E — Monthly</t>
+          <t xml:space="preserve">F — Monthly</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
@@ -9776,7 +10325,7 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">L — Peak, second route</t>
+          <t xml:space="preserve">G — Peak, second route</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
@@ -9801,12 +10350,12 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">EVIDENCE</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Each line below is computed from the raw Mercury data, not asserted</t>
         </is>
@@ -9823,18 +10372,9 @@
           <t xml:space="preserve">Transaction ids named on Mercury's 2025 statements against the ids in our pull</t>
         </is>
       </c>
-      <c r="C11" s="2">
-        <v>33.0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>33.0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.0</v>
-      </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXACT MATCH — 0 missing, 0 orphan</t>
+          <t xml:space="preserve">33 ↔ 33 — 0 missing, 0 orphan</t>
         </is>
       </c>
     </row>
@@ -9846,21 +10386,12 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The trap that puts a transaction in the wrong year: we pulled 2025 both ways and compared</t>
-        </is>
-      </c>
-      <c r="C12" s="2">
-        <v>38.0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>38.0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.0</v>
+          <t xml:space="preserve">The trap that puts a transaction in the wrong year — tested directly, not by comparing two pulls</t>
+        </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">IDENTICAL — no row straddles the year boundary</t>
+          <t xml:space="preserve">0 straddle the year, 5 straddle a day</t>
         </is>
       </c>
     </row>
@@ -9875,15 +10406,6 @@
           <t xml:space="preserve">Rows excluded because they failed or never posted</t>
         </is>
       </c>
-      <c r="C13" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.0</v>
-      </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE — all 38 rows posted</t>
@@ -9912,7 +10434,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZERO ALL YEAR — no rows</t>
+          <t xml:space="preserve">ZERO ALL YEAR — no transactions</t>
         </is>
       </c>
     </row>
@@ -9927,15 +10449,6 @@
           <t xml:space="preserve">Each 'Sent to card' row on the bank matched to its credit on the card ledger</t>
         </is>
       </c>
-      <c r="C15" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.0</v>
-      </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2 of 2 PAIRED</t>
@@ -9994,43 +10507,111 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Year-boundary margin, opening</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hours to the nearest transaction either side of 1 Jan 2025</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163.57 hours</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Year-boundary margin, closing</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hours to the nearest transaction either side of 1 Jan 2026</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.01 hours — wider than any timezone</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">NOTED, NOT RESOLVED</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The peak DATE is clock-sensitive</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The credit that set it posted 2.03 h before midnight UTC. The amount is clock-independent; on IST (+5:30) the date reads 1 August.</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31 July is the bank's own UTC basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Peak is an end-of-day figure</t>
         </is>
       </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A bank reports balances at the close of each day. The intra-day high in Mercury's own posting order is the same $35,157.93, so the distinction does not change the answer this year.</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">context</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A bank reports at each day's close. The intra-day high in Mercury's posting order is the same $35,157.93.</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">changes nothing this year</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Sent to card' is not card spend</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cash moved to settle the card, versus what the card bought. Equal this year only because the card was cleared in-year.</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">see 'Total expense incurred', Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Credit account has no statements</t>
         </is>
       </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mercury issues statements for the two bank accounts only, so the card ledger is corroborated by the mirrored payments and its zero balance rather than by a statement</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mercury issues statements for the two bank accounts only; the card ledger rests on the mirrored payments and its zero balance.</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">open</t>
         </is>
@@ -10163,97 +10744,107 @@
           <t xml:space="preserve">2025-05-11</t>
         </is>
       </c>
-      <c r="D4" s="2">
-        <v>0.0</v>
-      </c>
       <c r="E4" s="2">
         <v>0.0</v>
       </c>
-      <c r="F4" s="2">
-        <v>0.0</v>
-      </c>
       <c r="G4" s="2">
         <v>0.0</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">did not exist on 1 January 2025 — opened 11 May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">TOTAL BANK BALANCE</t>
         </is>
       </c>
-      <c r="D6" s="3">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking and savings; the card is a liability, not a balance</t>
+        </is>
+      </c>
+      <c r="D7" s="3">
+        <f>SUM(D2:D4)</f>
         <v>11053.84</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E7" s="3">
+        <f>SUM(E2:E4)</f>
         <v>32120.51</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F7" s="3">
+        <f>SUM(F2:F4)</f>
         <v>21066.67</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G7" s="3">
+        <f>SUM(G2:G3)</f>
         <v>35322.1</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Legal name</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GCALIT LLC</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">EIN</t>
+          <t xml:space="preserve">Legal name</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">61-2005202</t>
+          <t xml:space="preserve">GCALIT LLC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registered address</t>
+          <t xml:space="preserve">EIN</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309 Coffeen Avenue, Ste 1200, Sheridan WY, 82801</t>
+          <t xml:space="preserve">61-2005202</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Routing number</t>
+          <t xml:space="preserve">Registered address</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Held by Mercury; deliberately not published on this page</t>
+          <t xml:space="preserve">1309 Coffeen Avenue, Ste 1200, Sheridan WY, 82801</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Routing number</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Held by Mercury; deliberately not published on this page</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Data pulled</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-28 from the Mercury API, read-only</t>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-28 from the Mercury API, read-only. All dates UTC.</t>
         </is>
       </c>
     </row>
